--- a/05_תוצרים/לוח_זמנים_שלונסקי_53_ישראל_פועלים_ערבים.xlsx
+++ b/05_תוצרים/לוח_זמנים_שלונסקי_53_ישראל_פועלים_ערבים.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="342">
   <si>
     <t>לוח שנה וחגים – ישראל (תשפ"ז, נובמבר 2026 – יולי 2027)</t>
   </si>
@@ -343,6 +343,24 @@
     <t>14.01</t>
   </si>
   <si>
+    <t>A035</t>
+  </si>
+  <si>
+    <t>אישור יועץ האיטום לשיטת העבודה (לפני תחילת איטום)</t>
+  </si>
+  <si>
+    <t>10.01, 10.04</t>
+  </si>
+  <si>
+    <t>A040</t>
+  </si>
+  <si>
+    <t>החלטת המזמין הסופית בכתב על תריסים חשמליים (תנאי להנחת תשתית חשמל)</t>
+  </si>
+  <si>
+    <t>06.03</t>
+  </si>
+  <si>
     <t>A050</t>
   </si>
   <si>
@@ -367,10 +385,10 @@
     <t>S010</t>
   </si>
   <si>
-    <t>התארגנות אתר, גידור, חיבורי מים וחשמל זמניים, מכולת פסולת</t>
-  </si>
-  <si>
-    <t>01.01–01.04, 01.07</t>
+    <t>התארגנות אתר, גידור, חיבורי מים וחשמל זמניים, מכולת פסולת וניקיון שוטף</t>
+  </si>
+  <si>
+    <t>01.01–01.04, 01.07, 01.08</t>
   </si>
   <si>
     <t>S020</t>
@@ -385,7 +403,7 @@
     <t>S030</t>
   </si>
   <si>
-    <t>אישור כתוב של המתכננת למעבר להריסות</t>
+    <t>אישור כתוב של המתכננת והקונסטרוקטור למעבר להריסות (כולל סימון האלמנטים להריסה)</t>
   </si>
   <si>
     <t>הריסות ופירוקים</t>
@@ -397,7 +415,7 @@
     <t>פירוק חלונות, דלתות, כלים סניטריים, ארונות, מיזוג, חשמל וצנרת גלויה</t>
   </si>
   <si>
-    <t>02.06–02.13</t>
+    <t>02.06–02.14</t>
   </si>
   <si>
     <t>D020</t>
@@ -523,6 +541,12 @@
     <t>03.01</t>
   </si>
   <si>
+    <t>K035</t>
+  </si>
+  <si>
+    <t>בדיקת ריתוכי שלד הפלדה (פרגולה) על ידי בודק ריתוכים מוסמך</t>
+  </si>
+  <si>
     <t>K040</t>
   </si>
   <si>
@@ -568,6 +592,15 @@
     <t>06.01–06.06, 06.10, 06.11, 07.11, 07.20</t>
   </si>
   <si>
+    <t>EXT2</t>
+  </si>
+  <si>
+    <t>על ידי אחרים: צנרת מיזוג וניקוז ותשתית תקשורת, מיגון ושמע (לפני סגירת גבס)</t>
+  </si>
+  <si>
+    <t>(מחוץ להיקף)</t>
+  </si>
+  <si>
     <t>Q010</t>
   </si>
   <si>
@@ -649,13 +682,10 @@
     <t>חזית ופיתוח חיצוני</t>
   </si>
   <si>
-    <t>EXT1</t>
-  </si>
-  <si>
-    <t>על ידי אחרים: אלומיניום ודלתות – אספקה והתקנה</t>
-  </si>
-  <si>
-    <t>(מחוץ להיקף)</t>
+    <t>EXT5</t>
+  </si>
+  <si>
+    <t>על ידי אחרים: פרפט, איטום וקופינג בגג (פרק 11 במפרט – מחוץ להיקף)</t>
   </si>
   <si>
     <t>X020</t>
@@ -664,13 +694,34 @@
     <t>הכנת תשתית וטיח צבעוני לחזיתות (225 מ"ר)</t>
   </si>
   <si>
-    <t>Z010</t>
-  </si>
-  <si>
-    <t>אדני חלונות ואיטום חלונות</t>
-  </si>
-  <si>
-    <t>12.01, 12.02, 12.04</t>
+    <t>EXT1a</t>
+  </si>
+  <si>
+    <t>מדידה סופית בשטח לאחר טיח חיצוני ואישור לוח האלומיניום והדלתות (המזמין/ספק)</t>
+  </si>
+  <si>
+    <t>EXT1b</t>
+  </si>
+  <si>
+    <t>על ידי אחרים: אספקה והתקנת אלומיניום (R1–R26), דלתות ושערים</t>
+  </si>
+  <si>
+    <t>Z010a</t>
+  </si>
+  <si>
+    <t>אדני חלונות פנימיים וחיצוניים (לאחר אישור לוח האלומיניום)</t>
+  </si>
+  <si>
+    <t>12.01, 12.02</t>
+  </si>
+  <si>
+    <t>Z010b</t>
+  </si>
+  <si>
+    <t>איטום חלונות ובדיקת מים לספי חוץ (לאחר התקנת האלומיניום)</t>
+  </si>
+  <si>
+    <t>12.04</t>
   </si>
   <si>
     <t>X030</t>
@@ -694,13 +745,19 @@
     <t>T010</t>
   </si>
   <si>
+    <t>T020</t>
+  </si>
+  <si>
+    <t>EXT3</t>
+  </si>
+  <si>
+    <t>על ידי אחרים: התקנת יחידות מיזוג, בדיקות ואקום ולחץ ואישור המיזוג (לפני טיח וצבע בחדר)</t>
+  </si>
+  <si>
     <t>ריצוף פנים 120×120 ו-120×60 ס"מ</t>
   </si>
   <si>
     <t>13.01, 13.02</t>
-  </si>
-  <si>
-    <t>T020</t>
   </si>
   <si>
     <t>חיפוי קירות מקלחות (121 מ"ר)</t>
@@ -1576,7 +1633,7 @@
     <tabColor rgb="FF0038B8"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CI94"/>
+  <dimension ref="A1:CI102"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.7109375" customWidth="1"/>
@@ -2486,7 +2543,7 @@
       <c r="J13" s="15"/>
       <c r="K13" s="15"/>
       <c r="L13" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F13,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G13,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H13,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I13,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J13,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K13,$A$12:$A$87,0)),0))</f>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F13,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G13,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H13,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I13,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J13,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K13,$A$12:$A$95,0)),0))</f>
         <v>46333</v>
       </c>
       <c r="M13" s="18">
@@ -2530,7 +2587,7 @@
       <c r="J14" s="15"/>
       <c r="K14" s="15"/>
       <c r="L14" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F14,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G14,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H14,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I14,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J14,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K14,$A$12:$A$87,0)),0))</f>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F14,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G14,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H14,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I14,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J14,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K14,$A$12:$A$95,0)),0))</f>
         <v>46334</v>
       </c>
       <c r="M14" s="18">
@@ -2572,7 +2629,7 @@
       <c r="J15" s="15"/>
       <c r="K15" s="15"/>
       <c r="L15" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F15,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G15,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H15,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I15,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J15,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K15,$A$12:$A$87,0)),0))</f>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F15,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G15,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H15,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I15,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J15,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K15,$A$12:$A$95,0)),0))</f>
         <v>46334</v>
       </c>
       <c r="M15" s="18">
@@ -2614,7 +2671,7 @@
       <c r="J16" s="15"/>
       <c r="K16" s="15"/>
       <c r="L16" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F16,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G16,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H16,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I16,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J16,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K16,$A$12:$A$87,0)),0))</f>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F16,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G16,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H16,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I16,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J16,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K16,$A$12:$A$95,0)),0))</f>
         <v>46334</v>
       </c>
       <c r="M16" s="18">
@@ -2658,7 +2715,7 @@
       <c r="J17" s="15"/>
       <c r="K17" s="15"/>
       <c r="L17" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F17,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G17,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H17,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I17,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J17,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K17,$A$12:$A$87,0)),0))</f>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F17,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G17,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H17,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I17,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J17,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K17,$A$12:$A$95,0)),0))</f>
         <v>46334</v>
       </c>
       <c r="M17" s="18">
@@ -2700,7 +2757,7 @@
       <c r="J18" s="15"/>
       <c r="K18" s="15"/>
       <c r="L18" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F18,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G18,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H18,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I18,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J18,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K18,$A$12:$A$87,0)),0))</f>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F18,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G18,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H18,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I18,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J18,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K18,$A$12:$A$95,0)),0))</f>
         <v>46334</v>
       </c>
       <c r="M18" s="18">
@@ -2727,14 +2784,14 @@
         <v>109</v>
       </c>
       <c r="D19" s="17">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E19" s="15">
         <f>D19</f>
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="G19" s="15"/>
       <c r="H19" s="15"/>
@@ -2742,23 +2799,23 @@
       <c r="J19" s="15"/>
       <c r="K19" s="15"/>
       <c r="L19" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F19,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G19,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H19,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I19,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J19,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K19,$A$12:$A$87,0)),0))</f>
-        <v>46348</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F19,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G19,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H19,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I19,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J19,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K19,$A$12:$A$95,0)),0))</f>
+        <v>46334</v>
       </c>
       <c r="M19" s="18">
         <f>IF(E19=0,IF(COUNTA(F19:K19)=0,$D$2,L19),WORKDAY.INTL(L19,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46349</v>
+        <v>46335</v>
       </c>
       <c r="N19" s="18">
         <f>IF(E19=0,M19,WORKDAY.INTL(M19,E19-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46376</v>
+        <v>46337</v>
       </c>
       <c r="O19" s="19"/>
       <c r="P19" s="15" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="1:87">
+    <row r="20" spans="1:87" ht="26" customHeight="1">
       <c r="A20" s="15" t="s">
         <v>110</v>
       </c>
@@ -2769,14 +2826,14 @@
         <v>112</v>
       </c>
       <c r="D20" s="17">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E20" s="15">
         <f>D20</f>
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="G20" s="15"/>
       <c r="H20" s="15"/>
@@ -2784,16 +2841,16 @@
       <c r="J20" s="15"/>
       <c r="K20" s="15"/>
       <c r="L20" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F20,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G20,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H20,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I20,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J20,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K20,$A$12:$A$87,0)),0))</f>
-        <v>46348</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F20,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G20,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H20,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I20,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J20,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K20,$A$12:$A$95,0)),0))</f>
+        <v>46334</v>
       </c>
       <c r="M20" s="18">
         <f>IF(E20=0,IF(COUNTA(F20:K20)=0,$D$2,L20),WORKDAY.INTL(L20,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46349</v>
+        <v>46335</v>
       </c>
       <c r="N20" s="18">
         <f>IF(E20=0,M20,WORKDAY.INTL(M20,E20-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46376</v>
+        <v>46341</v>
       </c>
       <c r="O20" s="19"/>
       <c r="P20" s="15" t="s">
@@ -2801,124 +2858,74 @@
       </c>
     </row>
     <row r="21" spans="1:87">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="13"/>
-      <c r="M21" s="13"/>
-      <c r="N21" s="13"/>
-      <c r="O21" s="13"/>
-      <c r="P21" s="13"/>
-      <c r="R21" s="14"/>
-      <c r="S21" s="14"/>
-      <c r="T21" s="14"/>
-      <c r="U21" s="14"/>
-      <c r="V21" s="14"/>
-      <c r="W21" s="14"/>
-      <c r="X21" s="14"/>
-      <c r="Y21" s="14"/>
-      <c r="Z21" s="14"/>
-      <c r="AA21" s="14"/>
-      <c r="AB21" s="14"/>
-      <c r="AC21" s="14"/>
-      <c r="AD21" s="14"/>
-      <c r="AE21" s="14"/>
-      <c r="AF21" s="14"/>
-      <c r="AG21" s="14"/>
-      <c r="AH21" s="14"/>
-      <c r="AI21" s="14"/>
-      <c r="AJ21" s="14"/>
-      <c r="AK21" s="14"/>
-      <c r="AL21" s="14"/>
-      <c r="AM21" s="14"/>
-      <c r="AN21" s="14"/>
-      <c r="AO21" s="14"/>
-      <c r="AP21" s="14"/>
-      <c r="AQ21" s="14"/>
-      <c r="AR21" s="14"/>
-      <c r="AS21" s="14"/>
-      <c r="AT21" s="14"/>
-      <c r="AU21" s="14"/>
-      <c r="AV21" s="14"/>
-      <c r="AW21" s="14"/>
-      <c r="AX21" s="14"/>
-      <c r="AY21" s="14"/>
-      <c r="AZ21" s="14"/>
-      <c r="BA21" s="14"/>
-      <c r="BB21" s="14"/>
-      <c r="BC21" s="14"/>
-      <c r="BD21" s="14"/>
-      <c r="BE21" s="14"/>
-      <c r="BF21" s="14"/>
-      <c r="BG21" s="14"/>
-      <c r="BH21" s="14"/>
-      <c r="BI21" s="14"/>
-      <c r="BJ21" s="14"/>
-      <c r="BK21" s="14"/>
-      <c r="BL21" s="14"/>
-      <c r="BM21" s="14"/>
-      <c r="BN21" s="14"/>
-      <c r="BO21" s="14"/>
-      <c r="BP21" s="14"/>
-      <c r="BQ21" s="14"/>
-      <c r="BR21" s="14"/>
-      <c r="BS21" s="14"/>
-      <c r="BT21" s="14"/>
-      <c r="BU21" s="14"/>
-      <c r="BV21" s="14"/>
-      <c r="BW21" s="14"/>
-      <c r="BX21" s="14"/>
-      <c r="BY21" s="14"/>
-      <c r="BZ21" s="14"/>
-      <c r="CA21" s="14"/>
-      <c r="CB21" s="14"/>
-      <c r="CC21" s="14"/>
-      <c r="CD21" s="14"/>
-      <c r="CE21" s="14"/>
-      <c r="CF21" s="14"/>
-      <c r="CG21" s="14"/>
-      <c r="CH21" s="14"/>
-      <c r="CI21" s="14"/>
+      <c r="B21" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="D21" s="17">
+        <v>20</v>
+      </c>
+      <c r="E21" s="15">
+        <f>D21</f>
+        <v>20</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="18">
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F21,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G21,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H21,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I21,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J21,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K21,$A$12:$A$95,0)),0))</f>
+        <v>46348</v>
+      </c>
+      <c r="M21" s="18">
+        <f>IF(E21=0,IF(COUNTA(F21:K21)=0,$D$2,L21),WORKDAY.INTL(L21,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
+        <v>46349</v>
+      </c>
+      <c r="N21" s="18">
+        <f>IF(E21=0,M21,WORKDAY.INTL(M21,E21-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
+        <v>46376</v>
+      </c>
+      <c r="O21" s="19"/>
+      <c r="P21" s="15" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="22" spans="1:87">
       <c r="A22" s="15" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D22" s="17">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E22" s="15">
-        <f>IF(D22=0,0,MAX(1,ROUNDUP(D22/$D$6,0)))</f>
-        <v>7</v>
+        <f>D22</f>
+        <v>20</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="G22" s="15" t="s">
-        <v>98</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="G22" s="15"/>
       <c r="H22" s="15"/>
       <c r="I22" s="15"/>
       <c r="J22" s="15"/>
       <c r="K22" s="15"/>
       <c r="L22" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F22,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G22,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H22,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I22,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J22,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K22,$A$12:$A$87,0)),0))</f>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F22,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G22,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H22,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I22,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J22,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K22,$A$12:$A$95,0)),0))</f>
         <v>46348</v>
       </c>
       <c r="M22" s="18">
@@ -2927,60 +2934,104 @@
       </c>
       <c r="N22" s="18">
         <f>IF(E22=0,M22,WORKDAY.INTL(M22,E22-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46357</v>
-      </c>
-      <c r="O22" s="19" t="s">
-        <v>90</v>
-      </c>
+        <v>46376</v>
+      </c>
+      <c r="O22" s="19"/>
       <c r="P22" s="15" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:87">
-      <c r="A23" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="B23" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="C23" s="16" t="s">
+      <c r="A23" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="D23" s="17">
-        <v>4</v>
-      </c>
-      <c r="E23" s="15">
-        <f>IF(D23=0,0,MAX(1,ROUNDUP(D23/$D$6,0)))</f>
-        <v>6</v>
-      </c>
-      <c r="F23" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="15"/>
-      <c r="K23" s="15"/>
-      <c r="L23" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F23,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G23,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H23,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I23,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J23,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K23,$A$12:$A$87,0)),0))</f>
-        <v>46357</v>
-      </c>
-      <c r="M23" s="18">
-        <f>IF(E23=0,IF(COUNTA(F23:K23)=0,$D$2,L23),WORKDAY.INTL(L23,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46358</v>
-      </c>
-      <c r="N23" s="18">
-        <f>IF(E23=0,M23,WORKDAY.INTL(M23,E23-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46365</v>
-      </c>
-      <c r="O23" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="P23" s="15" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="24" spans="1:87">
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="13"/>
+      <c r="M23" s="13"/>
+      <c r="N23" s="13"/>
+      <c r="O23" s="13"/>
+      <c r="P23" s="13"/>
+      <c r="R23" s="14"/>
+      <c r="S23" s="14"/>
+      <c r="T23" s="14"/>
+      <c r="U23" s="14"/>
+      <c r="V23" s="14"/>
+      <c r="W23" s="14"/>
+      <c r="X23" s="14"/>
+      <c r="Y23" s="14"/>
+      <c r="Z23" s="14"/>
+      <c r="AA23" s="14"/>
+      <c r="AB23" s="14"/>
+      <c r="AC23" s="14"/>
+      <c r="AD23" s="14"/>
+      <c r="AE23" s="14"/>
+      <c r="AF23" s="14"/>
+      <c r="AG23" s="14"/>
+      <c r="AH23" s="14"/>
+      <c r="AI23" s="14"/>
+      <c r="AJ23" s="14"/>
+      <c r="AK23" s="14"/>
+      <c r="AL23" s="14"/>
+      <c r="AM23" s="14"/>
+      <c r="AN23" s="14"/>
+      <c r="AO23" s="14"/>
+      <c r="AP23" s="14"/>
+      <c r="AQ23" s="14"/>
+      <c r="AR23" s="14"/>
+      <c r="AS23" s="14"/>
+      <c r="AT23" s="14"/>
+      <c r="AU23" s="14"/>
+      <c r="AV23" s="14"/>
+      <c r="AW23" s="14"/>
+      <c r="AX23" s="14"/>
+      <c r="AY23" s="14"/>
+      <c r="AZ23" s="14"/>
+      <c r="BA23" s="14"/>
+      <c r="BB23" s="14"/>
+      <c r="BC23" s="14"/>
+      <c r="BD23" s="14"/>
+      <c r="BE23" s="14"/>
+      <c r="BF23" s="14"/>
+      <c r="BG23" s="14"/>
+      <c r="BH23" s="14"/>
+      <c r="BI23" s="14"/>
+      <c r="BJ23" s="14"/>
+      <c r="BK23" s="14"/>
+      <c r="BL23" s="14"/>
+      <c r="BM23" s="14"/>
+      <c r="BN23" s="14"/>
+      <c r="BO23" s="14"/>
+      <c r="BP23" s="14"/>
+      <c r="BQ23" s="14"/>
+      <c r="BR23" s="14"/>
+      <c r="BS23" s="14"/>
+      <c r="BT23" s="14"/>
+      <c r="BU23" s="14"/>
+      <c r="BV23" s="14"/>
+      <c r="BW23" s="14"/>
+      <c r="BX23" s="14"/>
+      <c r="BY23" s="14"/>
+      <c r="BZ23" s="14"/>
+      <c r="CA23" s="14"/>
+      <c r="CB23" s="14"/>
+      <c r="CC23" s="14"/>
+      <c r="CD23" s="14"/>
+      <c r="CE23" s="14"/>
+      <c r="CF23" s="14"/>
+      <c r="CG23" s="14"/>
+      <c r="CH23" s="14"/>
+      <c r="CI23" s="14"/>
+    </row>
+    <row r="24" spans="1:87" ht="26" customHeight="1">
       <c r="A24" s="15" t="s">
         <v>120</v>
       </c>
@@ -2988,34 +3039,38 @@
         <v>121</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>89</v>
+        <v>122</v>
       </c>
       <c r="D24" s="17">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E24" s="15">
-        <f>D24</f>
-        <v>1</v>
+        <f>IF(D24=0,0,MAX(1,ROUNDUP(D24/$D$6,0)))</f>
+        <v>7</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
+        <v>96</v>
+      </c>
+      <c r="G24" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="H24" s="15" t="s">
+        <v>92</v>
+      </c>
       <c r="I24" s="15"/>
       <c r="J24" s="15"/>
       <c r="K24" s="15"/>
       <c r="L24" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F24,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G24,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H24,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I24,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J24,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K24,$A$12:$A$87,0)),0))</f>
-        <v>46365</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F24,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G24,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H24,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I24,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J24,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K24,$A$12:$A$95,0)),0))</f>
+        <v>46348</v>
       </c>
       <c r="M24" s="18">
         <f>IF(E24=0,IF(COUNTA(F24:K24)=0,$D$2,L24),WORKDAY.INTL(L24,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46366</v>
+        <v>46349</v>
       </c>
       <c r="N24" s="18">
         <f>IF(E24=0,M24,WORKDAY.INTL(M24,E24-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46366</v>
+        <v>46357</v>
       </c>
       <c r="O24" s="19" t="s">
         <v>90</v>
@@ -3025,114 +3080,68 @@
       </c>
     </row>
     <row r="25" spans="1:87">
-      <c r="A25" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
-      <c r="K25" s="13"/>
-      <c r="L25" s="13"/>
-      <c r="M25" s="13"/>
-      <c r="N25" s="13"/>
-      <c r="O25" s="13"/>
-      <c r="P25" s="13"/>
-      <c r="R25" s="14"/>
-      <c r="S25" s="14"/>
-      <c r="T25" s="14"/>
-      <c r="U25" s="14"/>
-      <c r="V25" s="14"/>
-      <c r="W25" s="14"/>
-      <c r="X25" s="14"/>
-      <c r="Y25" s="14"/>
-      <c r="Z25" s="14"/>
-      <c r="AA25" s="14"/>
-      <c r="AB25" s="14"/>
-      <c r="AC25" s="14"/>
-      <c r="AD25" s="14"/>
-      <c r="AE25" s="14"/>
-      <c r="AF25" s="14"/>
-      <c r="AG25" s="14"/>
-      <c r="AH25" s="14"/>
-      <c r="AI25" s="14"/>
-      <c r="AJ25" s="14"/>
-      <c r="AK25" s="14"/>
-      <c r="AL25" s="14"/>
-      <c r="AM25" s="14"/>
-      <c r="AN25" s="14"/>
-      <c r="AO25" s="14"/>
-      <c r="AP25" s="14"/>
-      <c r="AQ25" s="14"/>
-      <c r="AR25" s="14"/>
-      <c r="AS25" s="14"/>
-      <c r="AT25" s="14"/>
-      <c r="AU25" s="14"/>
-      <c r="AV25" s="14"/>
-      <c r="AW25" s="14"/>
-      <c r="AX25" s="14"/>
-      <c r="AY25" s="14"/>
-      <c r="AZ25" s="14"/>
-      <c r="BA25" s="14"/>
-      <c r="BB25" s="14"/>
-      <c r="BC25" s="14"/>
-      <c r="BD25" s="14"/>
-      <c r="BE25" s="14"/>
-      <c r="BF25" s="14"/>
-      <c r="BG25" s="14"/>
-      <c r="BH25" s="14"/>
-      <c r="BI25" s="14"/>
-      <c r="BJ25" s="14"/>
-      <c r="BK25" s="14"/>
-      <c r="BL25" s="14"/>
-      <c r="BM25" s="14"/>
-      <c r="BN25" s="14"/>
-      <c r="BO25" s="14"/>
-      <c r="BP25" s="14"/>
-      <c r="BQ25" s="14"/>
-      <c r="BR25" s="14"/>
-      <c r="BS25" s="14"/>
-      <c r="BT25" s="14"/>
-      <c r="BU25" s="14"/>
-      <c r="BV25" s="14"/>
-      <c r="BW25" s="14"/>
-      <c r="BX25" s="14"/>
-      <c r="BY25" s="14"/>
-      <c r="BZ25" s="14"/>
-      <c r="CA25" s="14"/>
-      <c r="CB25" s="14"/>
-      <c r="CC25" s="14"/>
-      <c r="CD25" s="14"/>
-      <c r="CE25" s="14"/>
-      <c r="CF25" s="14"/>
-      <c r="CG25" s="14"/>
-      <c r="CH25" s="14"/>
-      <c r="CI25" s="14"/>
+      <c r="A25" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="D25" s="17">
+        <v>4</v>
+      </c>
+      <c r="E25" s="15">
+        <f>IF(D25=0,0,MAX(1,ROUNDUP(D25/$D$6,0)))</f>
+        <v>6</v>
+      </c>
+      <c r="F25" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="15"/>
+      <c r="J25" s="15"/>
+      <c r="K25" s="15"/>
+      <c r="L25" s="18">
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F25,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G25,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H25,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I25,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J25,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K25,$A$12:$A$95,0)),0))</f>
+        <v>46357</v>
+      </c>
+      <c r="M25" s="18">
+        <f>IF(E25=0,IF(COUNTA(F25:K25)=0,$D$2,L25),WORKDAY.INTL(L25,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
+        <v>46358</v>
+      </c>
+      <c r="N25" s="18">
+        <f>IF(E25=0,M25,WORKDAY.INTL(M25,E25-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
+        <v>46365</v>
+      </c>
+      <c r="O25" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="P25" s="15" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="26" spans="1:87" ht="26" customHeight="1">
       <c r="A26" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" s="17">
+        <v>1</v>
+      </c>
+      <c r="E26" s="15">
+        <f>D26</f>
+        <v>1</v>
+      </c>
+      <c r="F26" s="15" t="s">
         <v>123</v>
-      </c>
-      <c r="B26" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="D26" s="17">
-        <v>8</v>
-      </c>
-      <c r="E26" s="15">
-        <f>IF(D26=0,0,MAX(1,ROUNDUP(D26/$D$6,0)))</f>
-        <v>11</v>
-      </c>
-      <c r="F26" s="15" t="s">
-        <v>120</v>
       </c>
       <c r="G26" s="15"/>
       <c r="H26" s="15"/>
@@ -3140,16 +3149,16 @@
       <c r="J26" s="15"/>
       <c r="K26" s="15"/>
       <c r="L26" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F26,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G26,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H26,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I26,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J26,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K26,$A$12:$A$87,0)),0))</f>
-        <v>46366</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F26,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G26,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H26,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I26,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J26,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K26,$A$12:$A$95,0)),0))</f>
+        <v>46365</v>
       </c>
       <c r="M26" s="18">
         <f>IF(E26=0,IF(COUNTA(F26:K26)=0,$D$2,L26),WORKDAY.INTL(L26,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46369</v>
+        <v>46366</v>
       </c>
       <c r="N26" s="18">
         <f>IF(E26=0,M26,WORKDAY.INTL(M26,E26-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46383</v>
+        <v>46366</v>
       </c>
       <c r="O26" s="19" t="s">
         <v>90</v>
@@ -3159,48 +3168,96 @@
       </c>
     </row>
     <row r="27" spans="1:87">
-      <c r="A27" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>127</v>
-      </c>
-      <c r="C27" s="16" t="s">
+      <c r="A27" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="D27" s="17">
-        <v>3</v>
-      </c>
-      <c r="E27" s="15">
-        <f>IF(D27=0,0,MAX(1,ROUNDUP(D27/$D$6,0)))</f>
-        <v>5</v>
-      </c>
-      <c r="F27" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="15"/>
-      <c r="L27" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F27,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G27,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H27,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I27,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J27,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K27,$A$12:$A$87,0)),0))</f>
-        <v>46383</v>
-      </c>
-      <c r="M27" s="18">
-        <f>IF(E27=0,IF(COUNTA(F27:K27)=0,$D$2,L27),WORKDAY.INTL(L27,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46384</v>
-      </c>
-      <c r="N27" s="18">
-        <f>IF(E27=0,M27,WORKDAY.INTL(M27,E27-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46390</v>
-      </c>
-      <c r="O27" s="19"/>
-      <c r="P27" s="15" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="28" spans="1:87">
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="13"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="13"/>
+      <c r="L27" s="13"/>
+      <c r="M27" s="13"/>
+      <c r="N27" s="13"/>
+      <c r="O27" s="13"/>
+      <c r="P27" s="13"/>
+      <c r="R27" s="14"/>
+      <c r="S27" s="14"/>
+      <c r="T27" s="14"/>
+      <c r="U27" s="14"/>
+      <c r="V27" s="14"/>
+      <c r="W27" s="14"/>
+      <c r="X27" s="14"/>
+      <c r="Y27" s="14"/>
+      <c r="Z27" s="14"/>
+      <c r="AA27" s="14"/>
+      <c r="AB27" s="14"/>
+      <c r="AC27" s="14"/>
+      <c r="AD27" s="14"/>
+      <c r="AE27" s="14"/>
+      <c r="AF27" s="14"/>
+      <c r="AG27" s="14"/>
+      <c r="AH27" s="14"/>
+      <c r="AI27" s="14"/>
+      <c r="AJ27" s="14"/>
+      <c r="AK27" s="14"/>
+      <c r="AL27" s="14"/>
+      <c r="AM27" s="14"/>
+      <c r="AN27" s="14"/>
+      <c r="AO27" s="14"/>
+      <c r="AP27" s="14"/>
+      <c r="AQ27" s="14"/>
+      <c r="AR27" s="14"/>
+      <c r="AS27" s="14"/>
+      <c r="AT27" s="14"/>
+      <c r="AU27" s="14"/>
+      <c r="AV27" s="14"/>
+      <c r="AW27" s="14"/>
+      <c r="AX27" s="14"/>
+      <c r="AY27" s="14"/>
+      <c r="AZ27" s="14"/>
+      <c r="BA27" s="14"/>
+      <c r="BB27" s="14"/>
+      <c r="BC27" s="14"/>
+      <c r="BD27" s="14"/>
+      <c r="BE27" s="14"/>
+      <c r="BF27" s="14"/>
+      <c r="BG27" s="14"/>
+      <c r="BH27" s="14"/>
+      <c r="BI27" s="14"/>
+      <c r="BJ27" s="14"/>
+      <c r="BK27" s="14"/>
+      <c r="BL27" s="14"/>
+      <c r="BM27" s="14"/>
+      <c r="BN27" s="14"/>
+      <c r="BO27" s="14"/>
+      <c r="BP27" s="14"/>
+      <c r="BQ27" s="14"/>
+      <c r="BR27" s="14"/>
+      <c r="BS27" s="14"/>
+      <c r="BT27" s="14"/>
+      <c r="BU27" s="14"/>
+      <c r="BV27" s="14"/>
+      <c r="BW27" s="14"/>
+      <c r="BX27" s="14"/>
+      <c r="BY27" s="14"/>
+      <c r="BZ27" s="14"/>
+      <c r="CA27" s="14"/>
+      <c r="CB27" s="14"/>
+      <c r="CC27" s="14"/>
+      <c r="CD27" s="14"/>
+      <c r="CE27" s="14"/>
+      <c r="CF27" s="14"/>
+      <c r="CG27" s="14"/>
+      <c r="CH27" s="14"/>
+      <c r="CI27" s="14"/>
+    </row>
+    <row r="28" spans="1:87" ht="26" customHeight="1">
       <c r="A28" s="15" t="s">
         <v>129</v>
       </c>
@@ -3211,14 +3268,14 @@
         <v>131</v>
       </c>
       <c r="D28" s="17">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E28" s="15">
         <f>IF(D28=0,0,MAX(1,ROUNDUP(D28/$D$6,0)))</f>
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G28" s="15"/>
       <c r="H28" s="15"/>
@@ -3226,18 +3283,20 @@
       <c r="J28" s="15"/>
       <c r="K28" s="15"/>
       <c r="L28" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F28,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G28,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H28,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I28,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J28,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K28,$A$12:$A$87,0)),0))</f>
-        <v>46383</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F28,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G28,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H28,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I28,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J28,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K28,$A$12:$A$95,0)),0))</f>
+        <v>46366</v>
       </c>
       <c r="M28" s="18">
         <f>IF(E28=0,IF(COUNTA(F28:K28)=0,$D$2,L28),WORKDAY.INTL(L28,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46384</v>
+        <v>46369</v>
       </c>
       <c r="N28" s="18">
         <f>IF(E28=0,M28,WORKDAY.INTL(M28,E28-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46390</v>
-      </c>
-      <c r="O28" s="19"/>
+        <v>46383</v>
+      </c>
+      <c r="O28" s="19" t="s">
+        <v>90</v>
+      </c>
       <c r="P28" s="15" t="s">
         <v>91</v>
       </c>
@@ -3253,14 +3312,14 @@
         <v>134</v>
       </c>
       <c r="D29" s="17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E29" s="15">
         <f>IF(D29=0,0,MAX(1,ROUNDUP(D29/$D$6,0)))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="G29" s="15"/>
       <c r="H29" s="15"/>
@@ -3268,7 +3327,7 @@
       <c r="J29" s="15"/>
       <c r="K29" s="15"/>
       <c r="L29" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F29,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G29,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H29,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I29,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J29,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K29,$A$12:$A$87,0)),0))</f>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F29,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G29,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H29,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I29,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J29,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K29,$A$12:$A$95,0)),0))</f>
         <v>46383</v>
       </c>
       <c r="M29" s="18">
@@ -3277,7 +3336,7 @@
       </c>
       <c r="N29" s="18">
         <f>IF(E29=0,M29,WORKDAY.INTL(M29,E29-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46391</v>
+        <v>46390</v>
       </c>
       <c r="O29" s="19"/>
       <c r="P29" s="15" t="s">
@@ -3295,14 +3354,14 @@
         <v>137</v>
       </c>
       <c r="D30" s="17">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E30" s="15">
         <f>IF(D30=0,0,MAX(1,ROUNDUP(D30/$D$6,0)))</f>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="G30" s="15"/>
       <c r="H30" s="15"/>
@@ -3310,7 +3369,7 @@
       <c r="J30" s="15"/>
       <c r="K30" s="15"/>
       <c r="L30" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F30,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G30,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H30,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I30,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J30,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K30,$A$12:$A$87,0)),0))</f>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F30,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G30,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H30,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I30,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J30,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K30,$A$12:$A$95,0)),0))</f>
         <v>46383</v>
       </c>
       <c r="M30" s="18">
@@ -3319,11 +3378,9 @@
       </c>
       <c r="N30" s="18">
         <f>IF(E30=0,M30,WORKDAY.INTL(M30,E30-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46394</v>
-      </c>
-      <c r="O30" s="19" t="s">
-        <v>90</v>
-      </c>
+        <v>46390</v>
+      </c>
+      <c r="O30" s="19"/>
       <c r="P30" s="15" t="s">
         <v>91</v>
       </c>
@@ -3339,33 +3396,31 @@
         <v>140</v>
       </c>
       <c r="D31" s="17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E31" s="15">
         <f>IF(D31=0,0,MAX(1,ROUNDUP(D31/$D$6,0)))</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F31" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="G31" s="15" t="s">
-        <v>98</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="G31" s="15"/>
       <c r="H31" s="15"/>
       <c r="I31" s="15"/>
       <c r="J31" s="15"/>
       <c r="K31" s="15"/>
       <c r="L31" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F31,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G31,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H31,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I31,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J31,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K31,$A$12:$A$87,0)),0))</f>
-        <v>46366</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F31,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G31,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H31,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I31,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J31,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K31,$A$12:$A$95,0)),0))</f>
+        <v>46383</v>
       </c>
       <c r="M31" s="18">
         <f>IF(E31=0,IF(COUNTA(F31:K31)=0,$D$2,L31),WORKDAY.INTL(L31,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46369</v>
+        <v>46384</v>
       </c>
       <c r="N31" s="18">
         <f>IF(E31=0,M31,WORKDAY.INTL(M31,E31-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46377</v>
+        <v>46391</v>
       </c>
       <c r="O31" s="19"/>
       <c r="P31" s="15" t="s">
@@ -3380,17 +3435,17 @@
         <v>142</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D32" s="17">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E32" s="15">
-        <f>D32</f>
-        <v>1</v>
+        <f>IF(D32=0,0,MAX(1,ROUNDUP(D32/$D$6,0)))</f>
+        <v>9</v>
       </c>
       <c r="F32" s="15" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="G32" s="15"/>
       <c r="H32" s="15"/>
@@ -3398,89 +3453,87 @@
       <c r="J32" s="15"/>
       <c r="K32" s="15"/>
       <c r="L32" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F32,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G32,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H32,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I32,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J32,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K32,$A$12:$A$87,0)),0))</f>
-        <v>46377</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F32,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G32,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H32,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I32,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J32,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K32,$A$12:$A$95,0)),0))</f>
+        <v>46383</v>
       </c>
       <c r="M32" s="18">
         <f>IF(E32=0,IF(COUNTA(F32:K32)=0,$D$2,L32),WORKDAY.INTL(L32,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46378</v>
+        <v>46384</v>
       </c>
       <c r="N32" s="18">
         <f>IF(E32=0,M32,WORKDAY.INTL(M32,E32-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46378</v>
-      </c>
-      <c r="O32" s="19"/>
+        <v>46394</v>
+      </c>
+      <c r="O32" s="19" t="s">
+        <v>90</v>
+      </c>
       <c r="P32" s="15" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="33" spans="1:87" ht="26" customHeight="1">
+    <row r="33" spans="1:87">
       <c r="A33" s="15" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D33" s="17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E33" s="15">
         <f>IF(D33=0,0,MAX(1,ROUNDUP(D33/$D$6,0)))</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F33" s="15" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="H33" s="15" t="s">
-        <v>92</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="H33" s="15"/>
       <c r="I33" s="15"/>
       <c r="J33" s="15"/>
       <c r="K33" s="15"/>
       <c r="L33" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F33,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G33,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H33,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I33,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J33,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K33,$A$12:$A$87,0)),0))</f>
-        <v>46383</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F33,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G33,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H33,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I33,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J33,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K33,$A$12:$A$95,0)),0))</f>
+        <v>46366</v>
       </c>
       <c r="M33" s="18">
         <f>IF(E33=0,IF(COUNTA(F33:K33)=0,$D$2,L33),WORKDAY.INTL(L33,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46384</v>
+        <v>46369</v>
       </c>
       <c r="N33" s="18">
         <f>IF(E33=0,M33,WORKDAY.INTL(M33,E33-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46394</v>
-      </c>
-      <c r="O33" s="19" t="s">
-        <v>90</v>
-      </c>
+        <v>46377</v>
+      </c>
+      <c r="O33" s="19"/>
       <c r="P33" s="15" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:87">
       <c r="A34" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="C34" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="B34" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="C34" s="16" t="s">
-        <v>148</v>
-      </c>
       <c r="D34" s="17">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E34" s="15">
-        <f>IF(D34=0,0,MAX(1,ROUNDUP(D34/$D$6,0)))</f>
-        <v>10</v>
+        <f>D34</f>
+        <v>1</v>
       </c>
       <c r="F34" s="15" t="s">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="G34" s="15"/>
       <c r="H34" s="15"/>
@@ -3488,23 +3541,23 @@
       <c r="J34" s="15"/>
       <c r="K34" s="15"/>
       <c r="L34" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F34,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G34,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H34,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I34,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J34,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K34,$A$12:$A$87,0)),0))</f>
-        <v>46366</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F34,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G34,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H34,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I34,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J34,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K34,$A$12:$A$95,0)),0))</f>
+        <v>46377</v>
       </c>
       <c r="M34" s="18">
         <f>IF(E34=0,IF(COUNTA(F34:K34)=0,$D$2,L34),WORKDAY.INTL(L34,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46369</v>
+        <v>46378</v>
       </c>
       <c r="N34" s="18">
         <f>IF(E34=0,M34,WORKDAY.INTL(M34,E34-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46380</v>
+        <v>46378</v>
       </c>
       <c r="O34" s="19"/>
       <c r="P34" s="15" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="35" spans="1:87">
+    <row r="35" spans="1:87" ht="26" customHeight="1">
       <c r="A35" s="15" t="s">
         <v>149</v>
       </c>
@@ -3515,41 +3568,35 @@
         <v>151</v>
       </c>
       <c r="D35" s="17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E35" s="15">
         <f>IF(D35=0,0,MAX(1,ROUNDUP(D35/$D$6,0)))</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F35" s="15" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="G35" s="15" t="s">
         <v>129</v>
       </c>
       <c r="H35" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="I35" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="J35" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="K35" s="15" t="s">
-        <v>146</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="I35" s="15"/>
+      <c r="J35" s="15"/>
+      <c r="K35" s="15"/>
       <c r="L35" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F35,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G35,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H35,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I35,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J35,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K35,$A$12:$A$87,0)),0))</f>
-        <v>46394</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F35,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G35,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H35,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I35,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J35,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K35,$A$12:$A$95,0)),0))</f>
+        <v>46383</v>
       </c>
       <c r="M35" s="18">
         <f>IF(E35=0,IF(COUNTA(F35:K35)=0,$D$2,L35),WORKDAY.INTL(L35,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46397</v>
+        <v>46384</v>
       </c>
       <c r="N35" s="18">
         <f>IF(E35=0,M35,WORKDAY.INTL(M35,E35-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46404</v>
+        <v>46394</v>
       </c>
       <c r="O35" s="19" t="s">
         <v>90</v>
@@ -3566,17 +3613,17 @@
         <v>153</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>89</v>
+        <v>154</v>
       </c>
       <c r="D36" s="17">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E36" s="15">
-        <f>D36</f>
-        <v>2</v>
+        <f>IF(D36=0,0,MAX(1,ROUNDUP(D36/$D$6,0)))</f>
+        <v>10</v>
       </c>
       <c r="F36" s="15" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="G36" s="15"/>
       <c r="H36" s="15"/>
@@ -3584,133 +3631,95 @@
       <c r="J36" s="15"/>
       <c r="K36" s="15"/>
       <c r="L36" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F36,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G36,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H36,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I36,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J36,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K36,$A$12:$A$87,0)),0))</f>
-        <v>46404</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F36,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G36,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H36,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I36,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J36,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K36,$A$12:$A$95,0)),0))</f>
+        <v>46366</v>
       </c>
       <c r="M36" s="18">
         <f>IF(E36=0,IF(COUNTA(F36:K36)=0,$D$2,L36),WORKDAY.INTL(L36,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46405</v>
+        <v>46369</v>
       </c>
       <c r="N36" s="18">
         <f>IF(E36=0,M36,WORKDAY.INTL(M36,E36-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46406</v>
-      </c>
-      <c r="O36" s="19" t="s">
-        <v>90</v>
-      </c>
+        <v>46380</v>
+      </c>
+      <c r="O36" s="19"/>
       <c r="P36" s="15" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="37" spans="1:87">
-      <c r="A37" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
-      <c r="K37" s="13"/>
-      <c r="L37" s="13"/>
-      <c r="M37" s="13"/>
-      <c r="N37" s="13"/>
-      <c r="O37" s="13"/>
-      <c r="P37" s="13"/>
-      <c r="R37" s="14"/>
-      <c r="S37" s="14"/>
-      <c r="T37" s="14"/>
-      <c r="U37" s="14"/>
-      <c r="V37" s="14"/>
-      <c r="W37" s="14"/>
-      <c r="X37" s="14"/>
-      <c r="Y37" s="14"/>
-      <c r="Z37" s="14"/>
-      <c r="AA37" s="14"/>
-      <c r="AB37" s="14"/>
-      <c r="AC37" s="14"/>
-      <c r="AD37" s="14"/>
-      <c r="AE37" s="14"/>
-      <c r="AF37" s="14"/>
-      <c r="AG37" s="14"/>
-      <c r="AH37" s="14"/>
-      <c r="AI37" s="14"/>
-      <c r="AJ37" s="14"/>
-      <c r="AK37" s="14"/>
-      <c r="AL37" s="14"/>
-      <c r="AM37" s="14"/>
-      <c r="AN37" s="14"/>
-      <c r="AO37" s="14"/>
-      <c r="AP37" s="14"/>
-      <c r="AQ37" s="14"/>
-      <c r="AR37" s="14"/>
-      <c r="AS37" s="14"/>
-      <c r="AT37" s="14"/>
-      <c r="AU37" s="14"/>
-      <c r="AV37" s="14"/>
-      <c r="AW37" s="14"/>
-      <c r="AX37" s="14"/>
-      <c r="AY37" s="14"/>
-      <c r="AZ37" s="14"/>
-      <c r="BA37" s="14"/>
-      <c r="BB37" s="14"/>
-      <c r="BC37" s="14"/>
-      <c r="BD37" s="14"/>
-      <c r="BE37" s="14"/>
-      <c r="BF37" s="14"/>
-      <c r="BG37" s="14"/>
-      <c r="BH37" s="14"/>
-      <c r="BI37" s="14"/>
-      <c r="BJ37" s="14"/>
-      <c r="BK37" s="14"/>
-      <c r="BL37" s="14"/>
-      <c r="BM37" s="14"/>
-      <c r="BN37" s="14"/>
-      <c r="BO37" s="14"/>
-      <c r="BP37" s="14"/>
-      <c r="BQ37" s="14"/>
-      <c r="BR37" s="14"/>
-      <c r="BS37" s="14"/>
-      <c r="BT37" s="14"/>
-      <c r="BU37" s="14"/>
-      <c r="BV37" s="14"/>
-      <c r="BW37" s="14"/>
-      <c r="BX37" s="14"/>
-      <c r="BY37" s="14"/>
-      <c r="BZ37" s="14"/>
-      <c r="CA37" s="14"/>
-      <c r="CB37" s="14"/>
-      <c r="CC37" s="14"/>
-      <c r="CD37" s="14"/>
-      <c r="CE37" s="14"/>
-      <c r="CF37" s="14"/>
-      <c r="CG37" s="14"/>
-      <c r="CH37" s="14"/>
-      <c r="CI37" s="14"/>
+      <c r="A37" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="D37" s="17">
+        <v>4</v>
+      </c>
+      <c r="E37" s="15">
+        <f>IF(D37=0,0,MAX(1,ROUNDUP(D37/$D$6,0)))</f>
+        <v>6</v>
+      </c>
+      <c r="F37" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="G37" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="H37" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="I37" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="J37" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="K37" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="L37" s="18">
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F37,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G37,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H37,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I37,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J37,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K37,$A$12:$A$95,0)),0))</f>
+        <v>46394</v>
+      </c>
+      <c r="M37" s="18">
+        <f>IF(E37=0,IF(COUNTA(F37:K37)=0,$D$2,L37),WORKDAY.INTL(L37,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
+        <v>46397</v>
+      </c>
+      <c r="N37" s="18">
+        <f>IF(E37=0,M37,WORKDAY.INTL(M37,E37-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
+        <v>46404</v>
+      </c>
+      <c r="O37" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="P37" s="15" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="38" spans="1:87">
       <c r="A38" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D38" s="17">
+        <v>2</v>
+      </c>
+      <c r="E38" s="15">
+        <f>D38</f>
+        <v>2</v>
+      </c>
+      <c r="F38" s="15" t="s">
         <v>155</v>
-      </c>
-      <c r="B38" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="C38" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="D38" s="17">
-        <v>10</v>
-      </c>
-      <c r="E38" s="15">
-        <f>IF(D38=0,0,MAX(1,ROUNDUP(D38/$D$6,0)))</f>
-        <v>14</v>
-      </c>
-      <c r="F38" s="15" t="s">
-        <v>152</v>
       </c>
       <c r="G38" s="15"/>
       <c r="H38" s="15"/>
@@ -3718,65 +3727,113 @@
       <c r="J38" s="15"/>
       <c r="K38" s="15"/>
       <c r="L38" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F38,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G38,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H38,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I38,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J38,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K38,$A$12:$A$87,0)),0))</f>
-        <v>46406</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F38,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G38,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H38,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I38,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J38,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K38,$A$12:$A$95,0)),0))</f>
+        <v>46404</v>
       </c>
       <c r="M38" s="18">
         <f>IF(E38=0,IF(COUNTA(F38:K38)=0,$D$2,L38),WORKDAY.INTL(L38,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46407</v>
+        <v>46405</v>
       </c>
       <c r="N38" s="18">
         <f>IF(E38=0,M38,WORKDAY.INTL(M38,E38-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46426</v>
-      </c>
-      <c r="O38" s="19"/>
+        <v>46406</v>
+      </c>
+      <c r="O38" s="19" t="s">
+        <v>90</v>
+      </c>
       <c r="P38" s="15" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="39" spans="1:87">
-      <c r="A39" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="B39" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="C39" s="16" t="s">
+      <c r="A39" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="D39" s="17">
-        <v>15</v>
-      </c>
-      <c r="E39" s="15">
-        <f>IF(D39=0,0,MAX(1,ROUNDUP(D39/$D$6,0)))</f>
-        <v>21</v>
-      </c>
-      <c r="F39" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="G39" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="H39" s="15"/>
-      <c r="I39" s="15"/>
-      <c r="J39" s="15"/>
-      <c r="K39" s="15"/>
-      <c r="L39" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F39,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G39,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H39,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I39,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J39,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K39,$A$12:$A$87,0)),0))</f>
-        <v>46406</v>
-      </c>
-      <c r="M39" s="18">
-        <f>IF(E39=0,IF(COUNTA(F39:K39)=0,$D$2,L39),WORKDAY.INTL(L39,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46407</v>
-      </c>
-      <c r="N39" s="18">
-        <f>IF(E39=0,M39,WORKDAY.INTL(M39,E39-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46439</v>
-      </c>
-      <c r="O39" s="19"/>
-      <c r="P39" s="15" t="s">
-        <v>91</v>
-      </c>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
+      <c r="J39" s="13"/>
+      <c r="K39" s="13"/>
+      <c r="L39" s="13"/>
+      <c r="M39" s="13"/>
+      <c r="N39" s="13"/>
+      <c r="O39" s="13"/>
+      <c r="P39" s="13"/>
+      <c r="R39" s="14"/>
+      <c r="S39" s="14"/>
+      <c r="T39" s="14"/>
+      <c r="U39" s="14"/>
+      <c r="V39" s="14"/>
+      <c r="W39" s="14"/>
+      <c r="X39" s="14"/>
+      <c r="Y39" s="14"/>
+      <c r="Z39" s="14"/>
+      <c r="AA39" s="14"/>
+      <c r="AB39" s="14"/>
+      <c r="AC39" s="14"/>
+      <c r="AD39" s="14"/>
+      <c r="AE39" s="14"/>
+      <c r="AF39" s="14"/>
+      <c r="AG39" s="14"/>
+      <c r="AH39" s="14"/>
+      <c r="AI39" s="14"/>
+      <c r="AJ39" s="14"/>
+      <c r="AK39" s="14"/>
+      <c r="AL39" s="14"/>
+      <c r="AM39" s="14"/>
+      <c r="AN39" s="14"/>
+      <c r="AO39" s="14"/>
+      <c r="AP39" s="14"/>
+      <c r="AQ39" s="14"/>
+      <c r="AR39" s="14"/>
+      <c r="AS39" s="14"/>
+      <c r="AT39" s="14"/>
+      <c r="AU39" s="14"/>
+      <c r="AV39" s="14"/>
+      <c r="AW39" s="14"/>
+      <c r="AX39" s="14"/>
+      <c r="AY39" s="14"/>
+      <c r="AZ39" s="14"/>
+      <c r="BA39" s="14"/>
+      <c r="BB39" s="14"/>
+      <c r="BC39" s="14"/>
+      <c r="BD39" s="14"/>
+      <c r="BE39" s="14"/>
+      <c r="BF39" s="14"/>
+      <c r="BG39" s="14"/>
+      <c r="BH39" s="14"/>
+      <c r="BI39" s="14"/>
+      <c r="BJ39" s="14"/>
+      <c r="BK39" s="14"/>
+      <c r="BL39" s="14"/>
+      <c r="BM39" s="14"/>
+      <c r="BN39" s="14"/>
+      <c r="BO39" s="14"/>
+      <c r="BP39" s="14"/>
+      <c r="BQ39" s="14"/>
+      <c r="BR39" s="14"/>
+      <c r="BS39" s="14"/>
+      <c r="BT39" s="14"/>
+      <c r="BU39" s="14"/>
+      <c r="BV39" s="14"/>
+      <c r="BW39" s="14"/>
+      <c r="BX39" s="14"/>
+      <c r="BY39" s="14"/>
+      <c r="BZ39" s="14"/>
+      <c r="CA39" s="14"/>
+      <c r="CB39" s="14"/>
+      <c r="CC39" s="14"/>
+      <c r="CD39" s="14"/>
+      <c r="CE39" s="14"/>
+      <c r="CF39" s="14"/>
+      <c r="CG39" s="14"/>
+      <c r="CH39" s="14"/>
+      <c r="CI39" s="14"/>
     </row>
     <row r="40" spans="1:87">
       <c r="A40" s="15" t="s">
@@ -3789,11 +3846,11 @@
         <v>163</v>
       </c>
       <c r="D40" s="17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E40" s="15">
         <f>IF(D40=0,0,MAX(1,ROUNDUP(D40/$D$6,0)))</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F40" s="15" t="s">
         <v>158</v>
@@ -3804,16 +3861,16 @@
       <c r="J40" s="15"/>
       <c r="K40" s="15"/>
       <c r="L40" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F40,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G40,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H40,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I40,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J40,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K40,$A$12:$A$87,0)),0))</f>
-        <v>46439</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F40,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G40,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H40,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I40,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J40,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K40,$A$12:$A$95,0)),0))</f>
+        <v>46406</v>
       </c>
       <c r="M40" s="18">
         <f>IF(E40=0,IF(COUNTA(F40:K40)=0,$D$2,L40),WORKDAY.INTL(L40,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46440</v>
+        <v>46407</v>
       </c>
       <c r="N40" s="18">
         <f>IF(E40=0,M40,WORKDAY.INTL(M40,E40-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46461</v>
+        <v>46426</v>
       </c>
       <c r="O40" s="19"/>
       <c r="P40" s="15" t="s">
@@ -3831,14 +3888,14 @@
         <v>166</v>
       </c>
       <c r="D41" s="17">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="E41" s="15">
         <f>IF(D41=0,0,MAX(1,ROUNDUP(D41/$D$6,0)))</f>
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="F41" s="15" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="G41" s="15" t="s">
         <v>92</v>
@@ -3848,7 +3905,7 @@
       <c r="J41" s="15"/>
       <c r="K41" s="15"/>
       <c r="L41" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F41,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G41,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H41,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I41,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J41,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K41,$A$12:$A$87,0)),0))</f>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F41,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G41,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H41,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I41,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J41,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K41,$A$12:$A$95,0)),0))</f>
         <v>46406</v>
       </c>
       <c r="M41" s="18">
@@ -3857,7 +3914,7 @@
       </c>
       <c r="N41" s="18">
         <f>IF(E41=0,M41,WORKDAY.INTL(M41,E41-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46469</v>
+        <v>46439</v>
       </c>
       <c r="O41" s="19"/>
       <c r="P41" s="15" t="s">
@@ -3875,37 +3932,33 @@
         <v>169</v>
       </c>
       <c r="D42" s="17">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E42" s="15">
         <f>IF(D42=0,0,MAX(1,ROUNDUP(D42/$D$6,0)))</f>
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="F42" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="G42" s="15" t="s">
-        <v>92</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="G42" s="15"/>
       <c r="H42" s="15"/>
       <c r="I42" s="15"/>
       <c r="J42" s="15"/>
       <c r="K42" s="15"/>
       <c r="L42" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F42,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G42,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H42,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I42,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J42,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K42,$A$12:$A$87,0)),0))</f>
-        <v>46406</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F42,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G42,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H42,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I42,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J42,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K42,$A$12:$A$95,0)),0))</f>
+        <v>46439</v>
       </c>
       <c r="M42" s="18">
         <f>IF(E42=0,IF(COUNTA(F42:K42)=0,$D$2,L42),WORKDAY.INTL(L42,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46407</v>
+        <v>46440</v>
       </c>
       <c r="N42" s="18">
         <f>IF(E42=0,M42,WORKDAY.INTL(M42,E42-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46483</v>
-      </c>
-      <c r="O42" s="19" t="s">
-        <v>90</v>
-      </c>
+        <v>46461</v>
+      </c>
+      <c r="O42" s="19"/>
       <c r="P42" s="15" t="s">
         <v>91</v>
       </c>
@@ -3918,167 +3971,113 @@
         <v>171</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>89</v>
+        <v>172</v>
       </c>
       <c r="D43" s="17">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="E43" s="15">
-        <f>D43</f>
-        <v>2</v>
+        <f>IF(D43=0,0,MAX(1,ROUNDUP(D43/$D$6,0)))</f>
+        <v>38</v>
       </c>
       <c r="F43" s="15" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="G43" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="H43" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="I43" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="J43" s="15" t="s">
-        <v>167</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="H43" s="15"/>
+      <c r="I43" s="15"/>
+      <c r="J43" s="15"/>
       <c r="K43" s="15"/>
       <c r="L43" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F43,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G43,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H43,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I43,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J43,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K43,$A$12:$A$87,0)),0))</f>
-        <v>46483</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F43,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G43,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H43,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I43,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J43,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K43,$A$12:$A$95,0)),0))</f>
+        <v>46406</v>
       </c>
       <c r="M43" s="18">
         <f>IF(E43=0,IF(COUNTA(F43:K43)=0,$D$2,L43),WORKDAY.INTL(L43,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46484</v>
+        <v>46407</v>
       </c>
       <c r="N43" s="18">
         <f>IF(E43=0,M43,WORKDAY.INTL(M43,E43-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46485</v>
-      </c>
-      <c r="O43" s="19" t="s">
-        <v>90</v>
-      </c>
+        <v>46469</v>
+      </c>
+      <c r="O43" s="19"/>
       <c r="P43" s="15" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="44" spans="1:87">
-      <c r="A44" s="13" t="s">
+      <c r="A44" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="B44" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="C44" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="B44" s="13"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="13"/>
-      <c r="H44" s="13"/>
-      <c r="I44" s="13"/>
-      <c r="J44" s="13"/>
-      <c r="K44" s="13"/>
-      <c r="L44" s="13"/>
-      <c r="M44" s="13"/>
-      <c r="N44" s="13"/>
-      <c r="O44" s="13"/>
-      <c r="P44" s="13"/>
-      <c r="R44" s="14"/>
-      <c r="S44" s="14"/>
-      <c r="T44" s="14"/>
-      <c r="U44" s="14"/>
-      <c r="V44" s="14"/>
-      <c r="W44" s="14"/>
-      <c r="X44" s="14"/>
-      <c r="Y44" s="14"/>
-      <c r="Z44" s="14"/>
-      <c r="AA44" s="14"/>
-      <c r="AB44" s="14"/>
-      <c r="AC44" s="14"/>
-      <c r="AD44" s="14"/>
-      <c r="AE44" s="14"/>
-      <c r="AF44" s="14"/>
-      <c r="AG44" s="14"/>
-      <c r="AH44" s="14"/>
-      <c r="AI44" s="14"/>
-      <c r="AJ44" s="14"/>
-      <c r="AK44" s="14"/>
-      <c r="AL44" s="14"/>
-      <c r="AM44" s="14"/>
-      <c r="AN44" s="14"/>
-      <c r="AO44" s="14"/>
-      <c r="AP44" s="14"/>
-      <c r="AQ44" s="14"/>
-      <c r="AR44" s="14"/>
-      <c r="AS44" s="14"/>
-      <c r="AT44" s="14"/>
-      <c r="AU44" s="14"/>
-      <c r="AV44" s="14"/>
-      <c r="AW44" s="14"/>
-      <c r="AX44" s="14"/>
-      <c r="AY44" s="14"/>
-      <c r="AZ44" s="14"/>
-      <c r="BA44" s="14"/>
-      <c r="BB44" s="14"/>
-      <c r="BC44" s="14"/>
-      <c r="BD44" s="14"/>
-      <c r="BE44" s="14"/>
-      <c r="BF44" s="14"/>
-      <c r="BG44" s="14"/>
-      <c r="BH44" s="14"/>
-      <c r="BI44" s="14"/>
-      <c r="BJ44" s="14"/>
-      <c r="BK44" s="14"/>
-      <c r="BL44" s="14"/>
-      <c r="BM44" s="14"/>
-      <c r="BN44" s="14"/>
-      <c r="BO44" s="14"/>
-      <c r="BP44" s="14"/>
-      <c r="BQ44" s="14"/>
-      <c r="BR44" s="14"/>
-      <c r="BS44" s="14"/>
-      <c r="BT44" s="14"/>
-      <c r="BU44" s="14"/>
-      <c r="BV44" s="14"/>
-      <c r="BW44" s="14"/>
-      <c r="BX44" s="14"/>
-      <c r="BY44" s="14"/>
-      <c r="BZ44" s="14"/>
-      <c r="CA44" s="14"/>
-      <c r="CB44" s="14"/>
-      <c r="CC44" s="14"/>
-      <c r="CD44" s="14"/>
-      <c r="CE44" s="14"/>
-      <c r="CF44" s="14"/>
-      <c r="CG44" s="14"/>
-      <c r="CH44" s="14"/>
-      <c r="CI44" s="14"/>
+      <c r="D44" s="17">
+        <v>2</v>
+      </c>
+      <c r="E44" s="15">
+        <f>IF(D44=0,0,MAX(1,ROUNDUP(D44/$D$6,0)))</f>
+        <v>3</v>
+      </c>
+      <c r="F44" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="G44" s="15"/>
+      <c r="H44" s="15"/>
+      <c r="I44" s="15"/>
+      <c r="J44" s="15"/>
+      <c r="K44" s="15"/>
+      <c r="L44" s="18">
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F44,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G44,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H44,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I44,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J44,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K44,$A$12:$A$95,0)),0))</f>
+        <v>46469</v>
+      </c>
+      <c r="M44" s="18">
+        <f>IF(E44=0,IF(COUNTA(F44:K44)=0,$D$2,L44),WORKDAY.INTL(L44,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
+        <v>46470</v>
+      </c>
+      <c r="N44" s="18">
+        <f>IF(E44=0,M44,WORKDAY.INTL(M44,E44-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
+        <v>46474</v>
+      </c>
+      <c r="O44" s="19"/>
+      <c r="P44" s="15" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="45" spans="1:87">
       <c r="A45" s="15" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D45" s="17">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="E45" s="15">
         <f>IF(D45=0,0,MAX(1,ROUNDUP(D45/$D$6,0)))</f>
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="F45" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="G45" s="15"/>
+        <v>158</v>
+      </c>
+      <c r="G45" s="15" t="s">
+        <v>92</v>
+      </c>
       <c r="H45" s="15"/>
       <c r="I45" s="15"/>
       <c r="J45" s="15"/>
       <c r="K45" s="15"/>
       <c r="L45" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F45,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G45,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H45,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I45,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J45,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K45,$A$12:$A$87,0)),0))</f>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F45,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G45,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H45,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I45,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J45,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K45,$A$12:$A$95,0)),0))</f>
         <v>46406</v>
       </c>
       <c r="M45" s="18">
@@ -4087,120 +4086,178 @@
       </c>
       <c r="N45" s="18">
         <f>IF(E45=0,M45,WORKDAY.INTL(M45,E45-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46414</v>
-      </c>
-      <c r="O45" s="19"/>
+        <v>46483</v>
+      </c>
+      <c r="O45" s="19" t="s">
+        <v>90</v>
+      </c>
       <c r="P45" s="15" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="46" spans="1:87">
       <c r="A46" s="15" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>178</v>
+        <v>89</v>
       </c>
       <c r="D46" s="17">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E46" s="15">
-        <f>IF(D46=0,0,MAX(1,ROUNDUP(D46/$D$6,0)))</f>
-        <v>28</v>
+        <f>D46</f>
+        <v>2</v>
       </c>
       <c r="F46" s="15" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="G46" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="H46" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="I46" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="J46" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="H46" s="15"/>
-      <c r="I46" s="15"/>
-      <c r="J46" s="15"/>
-      <c r="K46" s="15"/>
+      <c r="K46" s="15" t="s">
+        <v>175</v>
+      </c>
       <c r="L46" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F46,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G46,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H46,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I46,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J46,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K46,$A$12:$A$87,0)),0))</f>
-        <v>46414</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F46,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G46,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H46,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I46,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J46,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K46,$A$12:$A$95,0)),0))</f>
+        <v>46483</v>
       </c>
       <c r="M46" s="18">
         <f>IF(E46=0,IF(COUNTA(F46:K46)=0,$D$2,L46),WORKDAY.INTL(L46,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46415</v>
+        <v>46484</v>
       </c>
       <c r="N46" s="18">
         <f>IF(E46=0,M46,WORKDAY.INTL(M46,E46-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46463</v>
-      </c>
-      <c r="O46" s="19"/>
+        <v>46485</v>
+      </c>
+      <c r="O46" s="19" t="s">
+        <v>90</v>
+      </c>
       <c r="P46" s="15" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="47" spans="1:87">
-      <c r="A47" s="15" t="s">
-        <v>179</v>
-      </c>
-      <c r="B47" s="16" t="s">
+      <c r="A47" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="C47" s="16" t="s">
-        <v>181</v>
-      </c>
-      <c r="D47" s="17">
-        <v>20</v>
-      </c>
-      <c r="E47" s="15">
-        <f>IF(D47=0,0,MAX(1,ROUNDUP(D47/$D$6,0)))</f>
-        <v>28</v>
-      </c>
-      <c r="F47" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="G47" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="H47" s="15"/>
-      <c r="I47" s="15"/>
-      <c r="J47" s="15"/>
-      <c r="K47" s="15"/>
-      <c r="L47" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F47,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G47,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H47,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I47,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J47,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K47,$A$12:$A$87,0)),0))</f>
-        <v>46414</v>
-      </c>
-      <c r="M47" s="18">
-        <f>IF(E47=0,IF(COUNTA(F47:K47)=0,$D$2,L47),WORKDAY.INTL(L47,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46415</v>
-      </c>
-      <c r="N47" s="18">
-        <f>IF(E47=0,M47,WORKDAY.INTL(M47,E47-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46463</v>
-      </c>
-      <c r="O47" s="19"/>
-      <c r="P47" s="15" t="s">
-        <v>91</v>
-      </c>
+      <c r="B47" s="13"/>
+      <c r="C47" s="13"/>
+      <c r="D47" s="13"/>
+      <c r="E47" s="13"/>
+      <c r="F47" s="13"/>
+      <c r="G47" s="13"/>
+      <c r="H47" s="13"/>
+      <c r="I47" s="13"/>
+      <c r="J47" s="13"/>
+      <c r="K47" s="13"/>
+      <c r="L47" s="13"/>
+      <c r="M47" s="13"/>
+      <c r="N47" s="13"/>
+      <c r="O47" s="13"/>
+      <c r="P47" s="13"/>
+      <c r="R47" s="14"/>
+      <c r="S47" s="14"/>
+      <c r="T47" s="14"/>
+      <c r="U47" s="14"/>
+      <c r="V47" s="14"/>
+      <c r="W47" s="14"/>
+      <c r="X47" s="14"/>
+      <c r="Y47" s="14"/>
+      <c r="Z47" s="14"/>
+      <c r="AA47" s="14"/>
+      <c r="AB47" s="14"/>
+      <c r="AC47" s="14"/>
+      <c r="AD47" s="14"/>
+      <c r="AE47" s="14"/>
+      <c r="AF47" s="14"/>
+      <c r="AG47" s="14"/>
+      <c r="AH47" s="14"/>
+      <c r="AI47" s="14"/>
+      <c r="AJ47" s="14"/>
+      <c r="AK47" s="14"/>
+      <c r="AL47" s="14"/>
+      <c r="AM47" s="14"/>
+      <c r="AN47" s="14"/>
+      <c r="AO47" s="14"/>
+      <c r="AP47" s="14"/>
+      <c r="AQ47" s="14"/>
+      <c r="AR47" s="14"/>
+      <c r="AS47" s="14"/>
+      <c r="AT47" s="14"/>
+      <c r="AU47" s="14"/>
+      <c r="AV47" s="14"/>
+      <c r="AW47" s="14"/>
+      <c r="AX47" s="14"/>
+      <c r="AY47" s="14"/>
+      <c r="AZ47" s="14"/>
+      <c r="BA47" s="14"/>
+      <c r="BB47" s="14"/>
+      <c r="BC47" s="14"/>
+      <c r="BD47" s="14"/>
+      <c r="BE47" s="14"/>
+      <c r="BF47" s="14"/>
+      <c r="BG47" s="14"/>
+      <c r="BH47" s="14"/>
+      <c r="BI47" s="14"/>
+      <c r="BJ47" s="14"/>
+      <c r="BK47" s="14"/>
+      <c r="BL47" s="14"/>
+      <c r="BM47" s="14"/>
+      <c r="BN47" s="14"/>
+      <c r="BO47" s="14"/>
+      <c r="BP47" s="14"/>
+      <c r="BQ47" s="14"/>
+      <c r="BR47" s="14"/>
+      <c r="BS47" s="14"/>
+      <c r="BT47" s="14"/>
+      <c r="BU47" s="14"/>
+      <c r="BV47" s="14"/>
+      <c r="BW47" s="14"/>
+      <c r="BX47" s="14"/>
+      <c r="BY47" s="14"/>
+      <c r="BZ47" s="14"/>
+      <c r="CA47" s="14"/>
+      <c r="CB47" s="14"/>
+      <c r="CC47" s="14"/>
+      <c r="CD47" s="14"/>
+      <c r="CE47" s="14"/>
+      <c r="CF47" s="14"/>
+      <c r="CG47" s="14"/>
+      <c r="CH47" s="14"/>
+      <c r="CI47" s="14"/>
     </row>
     <row r="48" spans="1:87">
       <c r="A48" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="B48" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="B48" s="16" t="s">
+      <c r="C48" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="C48" s="16" t="s">
-        <v>184</v>
-      </c>
       <c r="D48" s="17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E48" s="15">
-        <f>D48</f>
-        <v>3</v>
+        <f>IF(D48=0,0,MAX(1,ROUNDUP(D48/$D$6,0)))</f>
+        <v>6</v>
       </c>
       <c r="F48" s="15" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="G48" s="15"/>
       <c r="H48" s="15"/>
@@ -4208,16 +4265,16 @@
       <c r="J48" s="15"/>
       <c r="K48" s="15"/>
       <c r="L48" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F48,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G48,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H48,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I48,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J48,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K48,$A$12:$A$87,0)),0))</f>
-        <v>46463</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F48,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G48,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H48,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I48,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J48,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K48,$A$12:$A$95,0)),0))</f>
+        <v>46406</v>
       </c>
       <c r="M48" s="18">
         <f>IF(E48=0,IF(COUNTA(F48:K48)=0,$D$2,L48),WORKDAY.INTL(L48,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46464</v>
+        <v>46407</v>
       </c>
       <c r="N48" s="18">
         <f>IF(E48=0,M48,WORKDAY.INTL(M48,E48-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46468</v>
+        <v>46414</v>
       </c>
       <c r="O48" s="19"/>
       <c r="P48" s="15" t="s">
@@ -4226,40 +4283,42 @@
     </row>
     <row r="49" spans="1:87">
       <c r="A49" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="B49" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="B49" s="16" t="s">
+      <c r="C49" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="C49" s="16" t="s">
-        <v>187</v>
-      </c>
       <c r="D49" s="17">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E49" s="15">
-        <f>D49</f>
-        <v>3</v>
+        <f>IF(D49=0,0,MAX(1,ROUNDUP(D49/$D$6,0)))</f>
+        <v>28</v>
       </c>
       <c r="F49" s="15" t="s">
-        <v>179</v>
-      </c>
-      <c r="G49" s="15"/>
+        <v>158</v>
+      </c>
+      <c r="G49" s="15" t="s">
+        <v>181</v>
+      </c>
       <c r="H49" s="15"/>
       <c r="I49" s="15"/>
       <c r="J49" s="15"/>
       <c r="K49" s="15"/>
       <c r="L49" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F49,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G49,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H49,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I49,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J49,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K49,$A$12:$A$87,0)),0))</f>
-        <v>46463</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F49,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G49,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H49,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I49,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J49,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K49,$A$12:$A$95,0)),0))</f>
+        <v>46414</v>
       </c>
       <c r="M49" s="18">
         <f>IF(E49=0,IF(COUNTA(F49:K49)=0,$D$2,L49),WORKDAY.INTL(L49,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46464</v>
+        <v>46415</v>
       </c>
       <c r="N49" s="18">
         <f>IF(E49=0,M49,WORKDAY.INTL(M49,E49-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46468</v>
+        <v>46463</v>
       </c>
       <c r="O49" s="19"/>
       <c r="P49" s="15" t="s">
@@ -4267,162 +4326,114 @@
       </c>
     </row>
     <row r="50" spans="1:87">
-      <c r="A50" s="13" t="s">
+      <c r="A50" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="B50" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="13"/>
-      <c r="D50" s="13"/>
-      <c r="E50" s="13"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="13"/>
-      <c r="H50" s="13"/>
-      <c r="I50" s="13"/>
-      <c r="J50" s="13"/>
-      <c r="K50" s="13"/>
-      <c r="L50" s="13"/>
-      <c r="M50" s="13"/>
-      <c r="N50" s="13"/>
-      <c r="O50" s="13"/>
-      <c r="P50" s="13"/>
-      <c r="R50" s="14"/>
-      <c r="S50" s="14"/>
-      <c r="T50" s="14"/>
-      <c r="U50" s="14"/>
-      <c r="V50" s="14"/>
-      <c r="W50" s="14"/>
-      <c r="X50" s="14"/>
-      <c r="Y50" s="14"/>
-      <c r="Z50" s="14"/>
-      <c r="AA50" s="14"/>
-      <c r="AB50" s="14"/>
-      <c r="AC50" s="14"/>
-      <c r="AD50" s="14"/>
-      <c r="AE50" s="14"/>
-      <c r="AF50" s="14"/>
-      <c r="AG50" s="14"/>
-      <c r="AH50" s="14"/>
-      <c r="AI50" s="14"/>
-      <c r="AJ50" s="14"/>
-      <c r="AK50" s="14"/>
-      <c r="AL50" s="14"/>
-      <c r="AM50" s="14"/>
-      <c r="AN50" s="14"/>
-      <c r="AO50" s="14"/>
-      <c r="AP50" s="14"/>
-      <c r="AQ50" s="14"/>
-      <c r="AR50" s="14"/>
-      <c r="AS50" s="14"/>
-      <c r="AT50" s="14"/>
-      <c r="AU50" s="14"/>
-      <c r="AV50" s="14"/>
-      <c r="AW50" s="14"/>
-      <c r="AX50" s="14"/>
-      <c r="AY50" s="14"/>
-      <c r="AZ50" s="14"/>
-      <c r="BA50" s="14"/>
-      <c r="BB50" s="14"/>
-      <c r="BC50" s="14"/>
-      <c r="BD50" s="14"/>
-      <c r="BE50" s="14"/>
-      <c r="BF50" s="14"/>
-      <c r="BG50" s="14"/>
-      <c r="BH50" s="14"/>
-      <c r="BI50" s="14"/>
-      <c r="BJ50" s="14"/>
-      <c r="BK50" s="14"/>
-      <c r="BL50" s="14"/>
-      <c r="BM50" s="14"/>
-      <c r="BN50" s="14"/>
-      <c r="BO50" s="14"/>
-      <c r="BP50" s="14"/>
-      <c r="BQ50" s="14"/>
-      <c r="BR50" s="14"/>
-      <c r="BS50" s="14"/>
-      <c r="BT50" s="14"/>
-      <c r="BU50" s="14"/>
-      <c r="BV50" s="14"/>
-      <c r="BW50" s="14"/>
-      <c r="BX50" s="14"/>
-      <c r="BY50" s="14"/>
-      <c r="BZ50" s="14"/>
-      <c r="CA50" s="14"/>
-      <c r="CB50" s="14"/>
-      <c r="CC50" s="14"/>
-      <c r="CD50" s="14"/>
-      <c r="CE50" s="14"/>
-      <c r="CF50" s="14"/>
-      <c r="CG50" s="14"/>
-      <c r="CH50" s="14"/>
-      <c r="CI50" s="14"/>
-    </row>
-    <row r="51" spans="1:87">
+      <c r="C50" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="D50" s="17">
+        <v>20</v>
+      </c>
+      <c r="E50" s="15">
+        <f>IF(D50=0,0,MAX(1,ROUNDUP(D50/$D$6,0)))</f>
+        <v>28</v>
+      </c>
+      <c r="F50" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="G50" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="H50" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="I50" s="15"/>
+      <c r="J50" s="15"/>
+      <c r="K50" s="15"/>
+      <c r="L50" s="18">
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F50,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G50,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H50,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I50,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J50,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K50,$A$12:$A$95,0)),0))</f>
+        <v>46414</v>
+      </c>
+      <c r="M50" s="18">
+        <f>IF(E50=0,IF(COUNTA(F50:K50)=0,$D$2,L50),WORKDAY.INTL(L50,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
+        <v>46415</v>
+      </c>
+      <c r="N50" s="18">
+        <f>IF(E50=0,M50,WORKDAY.INTL(M50,E50-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
+        <v>46463</v>
+      </c>
+      <c r="O50" s="19"/>
+      <c r="P50" s="15" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="51" spans="1:87" ht="26" customHeight="1">
       <c r="A51" s="15" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D51" s="17">
         <v>12</v>
       </c>
       <c r="E51" s="15">
-        <f>IF(D51=0,0,MAX(1,ROUNDUP(D51/$D$6,0)))</f>
-        <v>17</v>
+        <f>D51</f>
+        <v>12</v>
       </c>
       <c r="F51" s="15" t="s">
-        <v>182</v>
+        <v>158</v>
       </c>
       <c r="G51" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="H51" s="15" t="s">
-        <v>170</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="H51" s="15"/>
       <c r="I51" s="15"/>
       <c r="J51" s="15"/>
       <c r="K51" s="15"/>
       <c r="L51" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F51,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G51,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H51,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I51,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J51,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K51,$A$12:$A$87,0)),0))</f>
-        <v>46485</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F51,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G51,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H51,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I51,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J51,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K51,$A$12:$A$95,0)),0))</f>
+        <v>46414</v>
       </c>
       <c r="M51" s="18">
         <f>IF(E51=0,IF(COUNTA(F51:K51)=0,$D$2,L51),WORKDAY.INTL(L51,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46488</v>
+        <v>46415</v>
       </c>
       <c r="N51" s="18">
         <f>IF(E51=0,M51,WORKDAY.INTL(M51,E51-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46512</v>
-      </c>
-      <c r="O51" s="19" t="s">
-        <v>90</v>
-      </c>
+        <v>46433</v>
+      </c>
+      <c r="O51" s="19"/>
       <c r="P51" s="15" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="52" spans="1:87">
       <c r="A52" s="15" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D52" s="17">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E52" s="15">
-        <f>IF(D52=0,0,MAX(1,ROUNDUP(D52/$D$6,0)))</f>
-        <v>9</v>
+        <f>D52</f>
+        <v>3</v>
       </c>
       <c r="F52" s="15" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="G52" s="15"/>
       <c r="H52" s="15"/>
@@ -4430,43 +4441,41 @@
       <c r="J52" s="15"/>
       <c r="K52" s="15"/>
       <c r="L52" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F52,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G52,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H52,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I52,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J52,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K52,$A$12:$A$87,0)),0))</f>
-        <v>46512</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F52,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G52,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H52,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I52,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J52,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K52,$A$12:$A$95,0)),0))</f>
+        <v>46463</v>
       </c>
       <c r="M52" s="18">
         <f>IF(E52=0,IF(COUNTA(F52:K52)=0,$D$2,L52),WORKDAY.INTL(L52,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46513</v>
+        <v>46464</v>
       </c>
       <c r="N52" s="18">
         <f>IF(E52=0,M52,WORKDAY.INTL(M52,E52-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46531</v>
-      </c>
-      <c r="O52" s="19" t="s">
-        <v>90</v>
-      </c>
+        <v>46468</v>
+      </c>
+      <c r="O52" s="19"/>
       <c r="P52" s="15" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="53" spans="1:87">
       <c r="A53" s="15" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C53" s="16" t="s">
-        <v>89</v>
+        <v>198</v>
       </c>
       <c r="D53" s="17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E53" s="15">
         <f>D53</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F53" s="15" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="G53" s="15"/>
       <c r="H53" s="15"/>
@@ -4474,67 +4483,111 @@
       <c r="J53" s="15"/>
       <c r="K53" s="15"/>
       <c r="L53" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F53,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G53,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H53,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I53,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J53,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K53,$A$12:$A$87,0)),0))</f>
-        <v>46531</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F53,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G53,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H53,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I53,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J53,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K53,$A$12:$A$95,0)),0))</f>
+        <v>46463</v>
       </c>
       <c r="M53" s="18">
         <f>IF(E53=0,IF(COUNTA(F53:K53)=0,$D$2,L53),WORKDAY.INTL(L53,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46532</v>
+        <v>46464</v>
       </c>
       <c r="N53" s="18">
         <f>IF(E53=0,M53,WORKDAY.INTL(M53,E53-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46533</v>
-      </c>
-      <c r="O53" s="19" t="s">
-        <v>90</v>
-      </c>
+        <v>46468</v>
+      </c>
+      <c r="O53" s="19"/>
       <c r="P53" s="15" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="54" spans="1:87">
-      <c r="A54" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="B54" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="C54" s="16" t="s">
+      <c r="A54" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="D54" s="17">
-        <v>6</v>
-      </c>
-      <c r="E54" s="15">
-        <f>IF(D54=0,0,MAX(1,ROUNDUP(D54/$D$6,0)))</f>
-        <v>9</v>
-      </c>
-      <c r="F54" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="G54" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="H54" s="15"/>
-      <c r="I54" s="15"/>
-      <c r="J54" s="15"/>
-      <c r="K54" s="15"/>
-      <c r="L54" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F54,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G54,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H54,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I54,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J54,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K54,$A$12:$A$87,0)),0))</f>
-        <v>46468</v>
-      </c>
-      <c r="M54" s="18">
-        <f>IF(E54=0,IF(COUNTA(F54:K54)=0,$D$2,L54),WORKDAY.INTL(L54,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46469</v>
-      </c>
-      <c r="N54" s="18">
-        <f>IF(E54=0,M54,WORKDAY.INTL(M54,E54-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46481</v>
-      </c>
-      <c r="O54" s="19"/>
-      <c r="P54" s="15" t="s">
-        <v>91</v>
-      </c>
+      <c r="B54" s="13"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
+      <c r="K54" s="13"/>
+      <c r="L54" s="13"/>
+      <c r="M54" s="13"/>
+      <c r="N54" s="13"/>
+      <c r="O54" s="13"/>
+      <c r="P54" s="13"/>
+      <c r="R54" s="14"/>
+      <c r="S54" s="14"/>
+      <c r="T54" s="14"/>
+      <c r="U54" s="14"/>
+      <c r="V54" s="14"/>
+      <c r="W54" s="14"/>
+      <c r="X54" s="14"/>
+      <c r="Y54" s="14"/>
+      <c r="Z54" s="14"/>
+      <c r="AA54" s="14"/>
+      <c r="AB54" s="14"/>
+      <c r="AC54" s="14"/>
+      <c r="AD54" s="14"/>
+      <c r="AE54" s="14"/>
+      <c r="AF54" s="14"/>
+      <c r="AG54" s="14"/>
+      <c r="AH54" s="14"/>
+      <c r="AI54" s="14"/>
+      <c r="AJ54" s="14"/>
+      <c r="AK54" s="14"/>
+      <c r="AL54" s="14"/>
+      <c r="AM54" s="14"/>
+      <c r="AN54" s="14"/>
+      <c r="AO54" s="14"/>
+      <c r="AP54" s="14"/>
+      <c r="AQ54" s="14"/>
+      <c r="AR54" s="14"/>
+      <c r="AS54" s="14"/>
+      <c r="AT54" s="14"/>
+      <c r="AU54" s="14"/>
+      <c r="AV54" s="14"/>
+      <c r="AW54" s="14"/>
+      <c r="AX54" s="14"/>
+      <c r="AY54" s="14"/>
+      <c r="AZ54" s="14"/>
+      <c r="BA54" s="14"/>
+      <c r="BB54" s="14"/>
+      <c r="BC54" s="14"/>
+      <c r="BD54" s="14"/>
+      <c r="BE54" s="14"/>
+      <c r="BF54" s="14"/>
+      <c r="BG54" s="14"/>
+      <c r="BH54" s="14"/>
+      <c r="BI54" s="14"/>
+      <c r="BJ54" s="14"/>
+      <c r="BK54" s="14"/>
+      <c r="BL54" s="14"/>
+      <c r="BM54" s="14"/>
+      <c r="BN54" s="14"/>
+      <c r="BO54" s="14"/>
+      <c r="BP54" s="14"/>
+      <c r="BQ54" s="14"/>
+      <c r="BR54" s="14"/>
+      <c r="BS54" s="14"/>
+      <c r="BT54" s="14"/>
+      <c r="BU54" s="14"/>
+      <c r="BV54" s="14"/>
+      <c r="BW54" s="14"/>
+      <c r="BX54" s="14"/>
+      <c r="BY54" s="14"/>
+      <c r="BZ54" s="14"/>
+      <c r="CA54" s="14"/>
+      <c r="CB54" s="14"/>
+      <c r="CC54" s="14"/>
+      <c r="CD54" s="14"/>
+      <c r="CE54" s="14"/>
+      <c r="CF54" s="14"/>
+      <c r="CG54" s="14"/>
+      <c r="CH54" s="14"/>
+      <c r="CI54" s="14"/>
     </row>
     <row r="55" spans="1:87">
       <c r="A55" s="15" t="s">
@@ -4547,35 +4600,41 @@
         <v>202</v>
       </c>
       <c r="D55" s="17">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E55" s="15">
         <f>IF(D55=0,0,MAX(1,ROUNDUP(D55/$D$6,0)))</f>
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F55" s="15" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="G55" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="H55" s="15"/>
-      <c r="I55" s="15"/>
+        <v>196</v>
+      </c>
+      <c r="H55" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="I55" s="15" t="s">
+        <v>190</v>
+      </c>
       <c r="J55" s="15"/>
       <c r="K55" s="15"/>
       <c r="L55" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F55,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G55,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H55,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I55,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J55,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K55,$A$12:$A$87,0)),0))</f>
-        <v>46469</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F55,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G55,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H55,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I55,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J55,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K55,$A$12:$A$95,0)),0))</f>
+        <v>46485</v>
       </c>
       <c r="M55" s="18">
         <f>IF(E55=0,IF(COUNTA(F55:K55)=0,$D$2,L55),WORKDAY.INTL(L55,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46470</v>
+        <v>46488</v>
       </c>
       <c r="N55" s="18">
         <f>IF(E55=0,M55,WORKDAY.INTL(M55,E55-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46482</v>
-      </c>
-      <c r="O55" s="19"/>
+        <v>46512</v>
+      </c>
+      <c r="O55" s="19" t="s">
+        <v>90</v>
+      </c>
       <c r="P55" s="15" t="s">
         <v>91</v>
       </c>
@@ -4591,35 +4650,35 @@
         <v>205</v>
       </c>
       <c r="D56" s="17">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E56" s="15">
-        <f>D56</f>
-        <v>3</v>
+        <f>IF(D56=0,0,MAX(1,ROUNDUP(D56/$D$6,0)))</f>
+        <v>9</v>
       </c>
       <c r="F56" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="G56" s="15" t="s">
         <v>200</v>
       </c>
+      <c r="G56" s="15"/>
       <c r="H56" s="15"/>
       <c r="I56" s="15"/>
       <c r="J56" s="15"/>
       <c r="K56" s="15"/>
       <c r="L56" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F56,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G56,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H56,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I56,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J56,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K56,$A$12:$A$87,0)),0))</f>
-        <v>46482</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F56,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G56,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H56,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I56,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J56,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K56,$A$12:$A$95,0)),0))</f>
+        <v>46512</v>
       </c>
       <c r="M56" s="18">
         <f>IF(E56=0,IF(COUNTA(F56:K56)=0,$D$2,L56),WORKDAY.INTL(L56,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46483</v>
+        <v>46513</v>
       </c>
       <c r="N56" s="18">
         <f>IF(E56=0,M56,WORKDAY.INTL(M56,E56-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46485</v>
-      </c>
-      <c r="O56" s="19"/>
+        <v>46531</v>
+      </c>
+      <c r="O56" s="19" t="s">
+        <v>90</v>
+      </c>
       <c r="P56" s="15" t="s">
         <v>91</v>
       </c>
@@ -4635,11 +4694,11 @@
         <v>89</v>
       </c>
       <c r="D57" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57" s="15">
         <f>D57</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" s="15" t="s">
         <v>203</v>
@@ -4650,194 +4709,154 @@
       <c r="J57" s="15"/>
       <c r="K57" s="15"/>
       <c r="L57" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F57,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G57,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H57,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I57,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J57,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K57,$A$12:$A$87,0)),0))</f>
-        <v>46485</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F57,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G57,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H57,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I57,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J57,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K57,$A$12:$A$95,0)),0))</f>
+        <v>46531</v>
       </c>
       <c r="M57" s="18">
         <f>IF(E57=0,IF(COUNTA(F57:K57)=0,$D$2,L57),WORKDAY.INTL(L57,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46488</v>
+        <v>46532</v>
       </c>
       <c r="N57" s="18">
         <f>IF(E57=0,M57,WORKDAY.INTL(M57,E57-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46488</v>
-      </c>
-      <c r="O57" s="19"/>
+        <v>46533</v>
+      </c>
+      <c r="O57" s="19" t="s">
+        <v>90</v>
+      </c>
       <c r="P57" s="15" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="58" spans="1:87">
-      <c r="A58" s="13" t="s">
+      <c r="A58" s="15" t="s">
         <v>208</v>
       </c>
-      <c r="B58" s="13"/>
-      <c r="C58" s="13"/>
-      <c r="D58" s="13"/>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13"/>
-      <c r="G58" s="13"/>
-      <c r="H58" s="13"/>
-      <c r="I58" s="13"/>
-      <c r="J58" s="13"/>
-      <c r="K58" s="13"/>
-      <c r="L58" s="13"/>
-      <c r="M58" s="13"/>
-      <c r="N58" s="13"/>
-      <c r="O58" s="13"/>
-      <c r="P58" s="13"/>
-      <c r="R58" s="14"/>
-      <c r="S58" s="14"/>
-      <c r="T58" s="14"/>
-      <c r="U58" s="14"/>
-      <c r="V58" s="14"/>
-      <c r="W58" s="14"/>
-      <c r="X58" s="14"/>
-      <c r="Y58" s="14"/>
-      <c r="Z58" s="14"/>
-      <c r="AA58" s="14"/>
-      <c r="AB58" s="14"/>
-      <c r="AC58" s="14"/>
-      <c r="AD58" s="14"/>
-      <c r="AE58" s="14"/>
-      <c r="AF58" s="14"/>
-      <c r="AG58" s="14"/>
-      <c r="AH58" s="14"/>
-      <c r="AI58" s="14"/>
-      <c r="AJ58" s="14"/>
-      <c r="AK58" s="14"/>
-      <c r="AL58" s="14"/>
-      <c r="AM58" s="14"/>
-      <c r="AN58" s="14"/>
-      <c r="AO58" s="14"/>
-      <c r="AP58" s="14"/>
-      <c r="AQ58" s="14"/>
-      <c r="AR58" s="14"/>
-      <c r="AS58" s="14"/>
-      <c r="AT58" s="14"/>
-      <c r="AU58" s="14"/>
-      <c r="AV58" s="14"/>
-      <c r="AW58" s="14"/>
-      <c r="AX58" s="14"/>
-      <c r="AY58" s="14"/>
-      <c r="AZ58" s="14"/>
-      <c r="BA58" s="14"/>
-      <c r="BB58" s="14"/>
-      <c r="BC58" s="14"/>
-      <c r="BD58" s="14"/>
-      <c r="BE58" s="14"/>
-      <c r="BF58" s="14"/>
-      <c r="BG58" s="14"/>
-      <c r="BH58" s="14"/>
-      <c r="BI58" s="14"/>
-      <c r="BJ58" s="14"/>
-      <c r="BK58" s="14"/>
-      <c r="BL58" s="14"/>
-      <c r="BM58" s="14"/>
-      <c r="BN58" s="14"/>
-      <c r="BO58" s="14"/>
-      <c r="BP58" s="14"/>
-      <c r="BQ58" s="14"/>
-      <c r="BR58" s="14"/>
-      <c r="BS58" s="14"/>
-      <c r="BT58" s="14"/>
-      <c r="BU58" s="14"/>
-      <c r="BV58" s="14"/>
-      <c r="BW58" s="14"/>
-      <c r="BX58" s="14"/>
-      <c r="BY58" s="14"/>
-      <c r="BZ58" s="14"/>
-      <c r="CA58" s="14"/>
-      <c r="CB58" s="14"/>
-      <c r="CC58" s="14"/>
-      <c r="CD58" s="14"/>
-      <c r="CE58" s="14"/>
-      <c r="CF58" s="14"/>
-      <c r="CG58" s="14"/>
-      <c r="CH58" s="14"/>
-      <c r="CI58" s="14"/>
+      <c r="B58" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="C58" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="D58" s="17">
+        <v>6</v>
+      </c>
+      <c r="E58" s="15">
+        <f>IF(D58=0,0,MAX(1,ROUNDUP(D58/$D$6,0)))</f>
+        <v>9</v>
+      </c>
+      <c r="F58" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="G58" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="H58" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="I58" s="15"/>
+      <c r="J58" s="15"/>
+      <c r="K58" s="15"/>
+      <c r="L58" s="18">
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F58,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G58,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H58,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I58,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J58,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K58,$A$12:$A$95,0)),0))</f>
+        <v>46468</v>
+      </c>
+      <c r="M58" s="18">
+        <f>IF(E58=0,IF(COUNTA(F58:K58)=0,$D$2,L58),WORKDAY.INTL(L58,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
+        <v>46469</v>
+      </c>
+      <c r="N58" s="18">
+        <f>IF(E58=0,M58,WORKDAY.INTL(M58,E58-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
+        <v>46481</v>
+      </c>
+      <c r="O58" s="19"/>
+      <c r="P58" s="15" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="59" spans="1:87">
       <c r="A59" s="15" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B59" s="16" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C59" s="16" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D59" s="17">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="E59" s="15">
-        <f>D59</f>
-        <v>40</v>
+        <f>IF(D59=0,0,MAX(1,ROUNDUP(D59/$D$6,0)))</f>
+        <v>9</v>
       </c>
       <c r="F59" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="G59" s="15"/>
-      <c r="H59" s="15"/>
+        <v>170</v>
+      </c>
+      <c r="G59" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="H59" s="15" t="s">
+        <v>107</v>
+      </c>
       <c r="I59" s="15"/>
       <c r="J59" s="15"/>
       <c r="K59" s="15"/>
       <c r="L59" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F59,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G59,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H59,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I59,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J59,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K59,$A$12:$A$87,0)),0))</f>
-        <v>46406</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F59,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G59,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H59,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I59,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J59,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K59,$A$12:$A$95,0)),0))</f>
+        <v>46469</v>
       </c>
       <c r="M59" s="18">
         <f>IF(E59=0,IF(COUNTA(F59:K59)=0,$D$2,L59),WORKDAY.INTL(L59,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46407</v>
+        <v>46470</v>
       </c>
       <c r="N59" s="18">
         <f>IF(E59=0,M59,WORKDAY.INTL(M59,E59-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46471</v>
+        <v>46482</v>
       </c>
       <c r="O59" s="19"/>
       <c r="P59" s="15" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="60" spans="1:87">
       <c r="A60" s="15" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>106</v>
+        <v>216</v>
       </c>
       <c r="D60" s="17">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E60" s="15">
-        <f>IF(D60=0,0,MAX(1,ROUNDUP(D60/$D$6,0)))</f>
-        <v>28</v>
+        <f>D60</f>
+        <v>3</v>
       </c>
       <c r="F60" s="15" t="s">
-        <v>141</v>
+        <v>208</v>
       </c>
       <c r="G60" s="15" t="s">
-        <v>209</v>
-      </c>
-      <c r="H60" s="15" t="s">
-        <v>143</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="H60" s="15"/>
       <c r="I60" s="15"/>
       <c r="J60" s="15"/>
       <c r="K60" s="15"/>
       <c r="L60" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F60,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G60,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H60,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I60,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J60,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K60,$A$12:$A$87,0)),0))</f>
-        <v>46471</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F60,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G60,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H60,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I60,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J60,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K60,$A$12:$A$95,0)),0))</f>
+        <v>46482</v>
       </c>
       <c r="M60" s="18">
         <f>IF(E60=0,IF(COUNTA(F60:K60)=0,$D$2,L60),WORKDAY.INTL(L60,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46474</v>
+        <v>46483</v>
       </c>
       <c r="N60" s="18">
         <f>IF(E60=0,M60,WORKDAY.INTL(M60,E60-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46513</v>
+        <v>46485</v>
       </c>
       <c r="O60" s="19"/>
       <c r="P60" s="15" t="s">
@@ -4846,42 +4865,40 @@
     </row>
     <row r="61" spans="1:87">
       <c r="A61" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="B61" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="C61" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D61" s="17">
+        <v>1</v>
+      </c>
+      <c r="E61" s="15">
+        <f>D61</f>
+        <v>1</v>
+      </c>
+      <c r="F61" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="B61" s="16" t="s">
-        <v>215</v>
-      </c>
-      <c r="C61" s="16" t="s">
-        <v>216</v>
-      </c>
-      <c r="D61" s="17">
-        <v>8</v>
-      </c>
-      <c r="E61" s="15">
-        <f>IF(D61=0,0,MAX(1,ROUNDUP(D61/$D$6,0)))</f>
-        <v>11</v>
-      </c>
-      <c r="F61" s="15" t="s">
-        <v>209</v>
-      </c>
-      <c r="G61" s="15" t="s">
-        <v>212</v>
-      </c>
+      <c r="G61" s="15"/>
       <c r="H61" s="15"/>
       <c r="I61" s="15"/>
       <c r="J61" s="15"/>
       <c r="K61" s="15"/>
       <c r="L61" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F61,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G61,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H61,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I61,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J61,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K61,$A$12:$A$87,0)),0))</f>
-        <v>46513</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F61,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G61,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H61,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I61,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J61,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K61,$A$12:$A$95,0)),0))</f>
+        <v>46485</v>
       </c>
       <c r="M61" s="18">
         <f>IF(E61=0,IF(COUNTA(F61:K61)=0,$D$2,L61),WORKDAY.INTL(L61,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46516</v>
+        <v>46488</v>
       </c>
       <c r="N61" s="18">
         <f>IF(E61=0,M61,WORKDAY.INTL(M61,E61-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46534</v>
+        <v>46488</v>
       </c>
       <c r="O61" s="19"/>
       <c r="P61" s="15" t="s">
@@ -4889,229 +4906,223 @@
       </c>
     </row>
     <row r="62" spans="1:87">
-      <c r="A62" s="15" t="s">
-        <v>217</v>
-      </c>
-      <c r="B62" s="16" t="s">
-        <v>218</v>
-      </c>
-      <c r="C62" s="16" t="s">
-        <v>140</v>
-      </c>
-      <c r="D62" s="17">
-        <v>4</v>
-      </c>
-      <c r="E62" s="15">
-        <f>IF(D62=0,0,MAX(1,ROUNDUP(D62/$D$6,0)))</f>
-        <v>6</v>
-      </c>
-      <c r="F62" s="15" t="s">
-        <v>212</v>
-      </c>
-      <c r="G62" s="15" t="s">
-        <v>214</v>
-      </c>
-      <c r="H62" s="15"/>
-      <c r="I62" s="15"/>
-      <c r="J62" s="15"/>
-      <c r="K62" s="15"/>
-      <c r="L62" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F62,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G62,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H62,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I62,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J62,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K62,$A$12:$A$87,0)),0))</f>
-        <v>46534</v>
-      </c>
-      <c r="M62" s="18">
-        <f>IF(E62=0,IF(COUNTA(F62:K62)=0,$D$2,L62),WORKDAY.INTL(L62,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46537</v>
-      </c>
-      <c r="N62" s="18">
-        <f>IF(E62=0,M62,WORKDAY.INTL(M62,E62-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46544</v>
-      </c>
-      <c r="O62" s="19"/>
-      <c r="P62" s="15" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="63" spans="1:87">
-      <c r="A63" s="13" t="s">
+      <c r="A62" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="B63" s="13"/>
-      <c r="C63" s="13"/>
-      <c r="D63" s="13"/>
-      <c r="E63" s="13"/>
-      <c r="F63" s="13"/>
-      <c r="G63" s="13"/>
-      <c r="H63" s="13"/>
-      <c r="I63" s="13"/>
-      <c r="J63" s="13"/>
-      <c r="K63" s="13"/>
-      <c r="L63" s="13"/>
-      <c r="M63" s="13"/>
-      <c r="N63" s="13"/>
-      <c r="O63" s="13"/>
-      <c r="P63" s="13"/>
-      <c r="R63" s="14"/>
-      <c r="S63" s="14"/>
-      <c r="T63" s="14"/>
-      <c r="U63" s="14"/>
-      <c r="V63" s="14"/>
-      <c r="W63" s="14"/>
-      <c r="X63" s="14"/>
-      <c r="Y63" s="14"/>
-      <c r="Z63" s="14"/>
-      <c r="AA63" s="14"/>
-      <c r="AB63" s="14"/>
-      <c r="AC63" s="14"/>
-      <c r="AD63" s="14"/>
-      <c r="AE63" s="14"/>
-      <c r="AF63" s="14"/>
-      <c r="AG63" s="14"/>
-      <c r="AH63" s="14"/>
-      <c r="AI63" s="14"/>
-      <c r="AJ63" s="14"/>
-      <c r="AK63" s="14"/>
-      <c r="AL63" s="14"/>
-      <c r="AM63" s="14"/>
-      <c r="AN63" s="14"/>
-      <c r="AO63" s="14"/>
-      <c r="AP63" s="14"/>
-      <c r="AQ63" s="14"/>
-      <c r="AR63" s="14"/>
-      <c r="AS63" s="14"/>
-      <c r="AT63" s="14"/>
-      <c r="AU63" s="14"/>
-      <c r="AV63" s="14"/>
-      <c r="AW63" s="14"/>
-      <c r="AX63" s="14"/>
-      <c r="AY63" s="14"/>
-      <c r="AZ63" s="14"/>
-      <c r="BA63" s="14"/>
-      <c r="BB63" s="14"/>
-      <c r="BC63" s="14"/>
-      <c r="BD63" s="14"/>
-      <c r="BE63" s="14"/>
-      <c r="BF63" s="14"/>
-      <c r="BG63" s="14"/>
-      <c r="BH63" s="14"/>
-      <c r="BI63" s="14"/>
-      <c r="BJ63" s="14"/>
-      <c r="BK63" s="14"/>
-      <c r="BL63" s="14"/>
-      <c r="BM63" s="14"/>
-      <c r="BN63" s="14"/>
-      <c r="BO63" s="14"/>
-      <c r="BP63" s="14"/>
-      <c r="BQ63" s="14"/>
-      <c r="BR63" s="14"/>
-      <c r="BS63" s="14"/>
-      <c r="BT63" s="14"/>
-      <c r="BU63" s="14"/>
-      <c r="BV63" s="14"/>
-      <c r="BW63" s="14"/>
-      <c r="BX63" s="14"/>
-      <c r="BY63" s="14"/>
-      <c r="BZ63" s="14"/>
-      <c r="CA63" s="14"/>
-      <c r="CB63" s="14"/>
-      <c r="CC63" s="14"/>
-      <c r="CD63" s="14"/>
-      <c r="CE63" s="14"/>
-      <c r="CF63" s="14"/>
-      <c r="CG63" s="14"/>
-      <c r="CH63" s="14"/>
-      <c r="CI63" s="14"/>
+      <c r="B62" s="13"/>
+      <c r="C62" s="13"/>
+      <c r="D62" s="13"/>
+      <c r="E62" s="13"/>
+      <c r="F62" s="13"/>
+      <c r="G62" s="13"/>
+      <c r="H62" s="13"/>
+      <c r="I62" s="13"/>
+      <c r="J62" s="13"/>
+      <c r="K62" s="13"/>
+      <c r="L62" s="13"/>
+      <c r="M62" s="13"/>
+      <c r="N62" s="13"/>
+      <c r="O62" s="13"/>
+      <c r="P62" s="13"/>
+      <c r="R62" s="14"/>
+      <c r="S62" s="14"/>
+      <c r="T62" s="14"/>
+      <c r="U62" s="14"/>
+      <c r="V62" s="14"/>
+      <c r="W62" s="14"/>
+      <c r="X62" s="14"/>
+      <c r="Y62" s="14"/>
+      <c r="Z62" s="14"/>
+      <c r="AA62" s="14"/>
+      <c r="AB62" s="14"/>
+      <c r="AC62" s="14"/>
+      <c r="AD62" s="14"/>
+      <c r="AE62" s="14"/>
+      <c r="AF62" s="14"/>
+      <c r="AG62" s="14"/>
+      <c r="AH62" s="14"/>
+      <c r="AI62" s="14"/>
+      <c r="AJ62" s="14"/>
+      <c r="AK62" s="14"/>
+      <c r="AL62" s="14"/>
+      <c r="AM62" s="14"/>
+      <c r="AN62" s="14"/>
+      <c r="AO62" s="14"/>
+      <c r="AP62" s="14"/>
+      <c r="AQ62" s="14"/>
+      <c r="AR62" s="14"/>
+      <c r="AS62" s="14"/>
+      <c r="AT62" s="14"/>
+      <c r="AU62" s="14"/>
+      <c r="AV62" s="14"/>
+      <c r="AW62" s="14"/>
+      <c r="AX62" s="14"/>
+      <c r="AY62" s="14"/>
+      <c r="AZ62" s="14"/>
+      <c r="BA62" s="14"/>
+      <c r="BB62" s="14"/>
+      <c r="BC62" s="14"/>
+      <c r="BD62" s="14"/>
+      <c r="BE62" s="14"/>
+      <c r="BF62" s="14"/>
+      <c r="BG62" s="14"/>
+      <c r="BH62" s="14"/>
+      <c r="BI62" s="14"/>
+      <c r="BJ62" s="14"/>
+      <c r="BK62" s="14"/>
+      <c r="BL62" s="14"/>
+      <c r="BM62" s="14"/>
+      <c r="BN62" s="14"/>
+      <c r="BO62" s="14"/>
+      <c r="BP62" s="14"/>
+      <c r="BQ62" s="14"/>
+      <c r="BR62" s="14"/>
+      <c r="BS62" s="14"/>
+      <c r="BT62" s="14"/>
+      <c r="BU62" s="14"/>
+      <c r="BV62" s="14"/>
+      <c r="BW62" s="14"/>
+      <c r="BX62" s="14"/>
+      <c r="BY62" s="14"/>
+      <c r="BZ62" s="14"/>
+      <c r="CA62" s="14"/>
+      <c r="CB62" s="14"/>
+      <c r="CC62" s="14"/>
+      <c r="CD62" s="14"/>
+      <c r="CE62" s="14"/>
+      <c r="CF62" s="14"/>
+      <c r="CG62" s="14"/>
+      <c r="CH62" s="14"/>
+      <c r="CI62" s="14"/>
+    </row>
+    <row r="63" spans="1:87" ht="26" customHeight="1">
+      <c r="A63" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="B63" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="C63" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="D63" s="17">
+        <v>25</v>
+      </c>
+      <c r="E63" s="15">
+        <f>D63</f>
+        <v>25</v>
+      </c>
+      <c r="F63" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="G63" s="15"/>
+      <c r="H63" s="15"/>
+      <c r="I63" s="15"/>
+      <c r="J63" s="15"/>
+      <c r="K63" s="15"/>
+      <c r="L63" s="18">
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F63,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G63,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H63,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I63,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J63,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K63,$A$12:$A$95,0)),0))</f>
+        <v>46406</v>
+      </c>
+      <c r="M63" s="18">
+        <f>IF(E63=0,IF(COUNTA(F63:K63)=0,$D$2,L63),WORKDAY.INTL(L63,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
+        <v>46407</v>
+      </c>
+      <c r="N63" s="18">
+        <f>IF(E63=0,M63,WORKDAY.INTL(M63,E63-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
+        <v>46446</v>
+      </c>
+      <c r="O63" s="19"/>
+      <c r="P63" s="15" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="64" spans="1:87">
       <c r="A64" s="15" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B64" s="16" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>222</v>
+        <v>106</v>
       </c>
       <c r="D64" s="17">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E64" s="15">
         <f>IF(D64=0,0,MAX(1,ROUNDUP(D64/$D$6,0)))</f>
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F64" s="15" t="s">
-        <v>195</v>
+        <v>147</v>
       </c>
       <c r="G64" s="15" t="s">
-        <v>209</v>
-      </c>
-      <c r="H64" s="15"/>
+        <v>220</v>
+      </c>
+      <c r="H64" s="15" t="s">
+        <v>149</v>
+      </c>
       <c r="I64" s="15"/>
       <c r="J64" s="15"/>
       <c r="K64" s="15"/>
       <c r="L64" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F64,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G64,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H64,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I64,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J64,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K64,$A$12:$A$87,0)),0))</f>
-        <v>46533</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F64,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G64,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H64,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I64,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J64,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K64,$A$12:$A$95,0)),0))</f>
+        <v>46446</v>
       </c>
       <c r="M64" s="18">
         <f>IF(E64=0,IF(COUNTA(F64:K64)=0,$D$2,L64),WORKDAY.INTL(L64,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46534</v>
+        <v>46447</v>
       </c>
       <c r="N64" s="18">
         <f>IF(E64=0,M64,WORKDAY.INTL(M64,E64-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46558</v>
+        <v>46490</v>
       </c>
       <c r="O64" s="19"/>
       <c r="P64" s="15" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="65" spans="1:87">
+    <row r="65" spans="1:87" ht="26" customHeight="1">
       <c r="A65" s="15" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B65" s="16" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C65" s="16" t="s">
-        <v>225</v>
+        <v>192</v>
       </c>
       <c r="D65" s="17">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E65" s="15">
-        <f>IF(D65=0,0,MAX(1,ROUNDUP(D65/$D$6,0)))</f>
-        <v>19</v>
+        <f>D65</f>
+        <v>5</v>
       </c>
       <c r="F65" s="15" t="s">
-        <v>206</v>
-      </c>
-      <c r="G65" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="H65" s="15" t="s">
-        <v>110</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="G65" s="15"/>
+      <c r="H65" s="15"/>
       <c r="I65" s="15"/>
       <c r="J65" s="15"/>
       <c r="K65" s="15"/>
       <c r="L65" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F65,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G65,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H65,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I65,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J65,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K65,$A$12:$A$87,0)),0))</f>
-        <v>46533</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F65,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G65,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H65,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I65,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J65,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K65,$A$12:$A$95,0)),0))</f>
+        <v>46490</v>
       </c>
       <c r="M65" s="18">
         <f>IF(E65=0,IF(COUNTA(F65:K65)=0,$D$2,L65),WORKDAY.INTL(L65,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46534</v>
+        <v>46491</v>
       </c>
       <c r="N65" s="18">
         <f>IF(E65=0,M65,WORKDAY.INTL(M65,E65-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46560</v>
-      </c>
-      <c r="O65" s="19" t="s">
-        <v>90</v>
-      </c>
+        <v>46497</v>
+      </c>
+      <c r="O65" s="19"/>
       <c r="P65" s="15" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="66" spans="1:87">
@@ -5122,80 +5133,78 @@
         <v>227</v>
       </c>
       <c r="C66" s="16" t="s">
-        <v>228</v>
+        <v>192</v>
       </c>
       <c r="D66" s="17">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="E66" s="15">
-        <f>IF(D66=0,0,MAX(1,ROUNDUP(D66/$D$6,0)))</f>
-        <v>11</v>
+        <f>D66</f>
+        <v>40</v>
       </c>
       <c r="F66" s="15" t="s">
-        <v>206</v>
-      </c>
-      <c r="G66" s="15" t="s">
-        <v>110</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="G66" s="15"/>
       <c r="H66" s="15"/>
       <c r="I66" s="15"/>
       <c r="J66" s="15"/>
       <c r="K66" s="15"/>
       <c r="L66" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F66,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G66,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H66,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I66,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J66,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K66,$A$12:$A$87,0)),0))</f>
-        <v>46488</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F66,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G66,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H66,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I66,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J66,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K66,$A$12:$A$95,0)),0))</f>
+        <v>46497</v>
       </c>
       <c r="M66" s="18">
         <f>IF(E66=0,IF(COUNTA(F66:K66)=0,$D$2,L66),WORKDAY.INTL(L66,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46489</v>
+        <v>46498</v>
       </c>
       <c r="N66" s="18">
         <f>IF(E66=0,M66,WORKDAY.INTL(M66,E66-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46504</v>
+        <v>46561</v>
       </c>
       <c r="O66" s="19"/>
       <c r="P66" s="15" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="67" spans="1:87">
       <c r="A67" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="B67" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="B67" s="16" t="s">
+      <c r="C67" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="C67" s="16" t="s">
-        <v>231</v>
-      </c>
       <c r="D67" s="17">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E67" s="15">
         <f>IF(D67=0,0,MAX(1,ROUNDUP(D67/$D$6,0)))</f>
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F67" s="15" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="G67" s="15" t="s">
-        <v>110</v>
+        <v>222</v>
       </c>
       <c r="H67" s="15"/>
       <c r="I67" s="15"/>
       <c r="J67" s="15"/>
       <c r="K67" s="15"/>
       <c r="L67" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F67,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G67,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H67,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I67,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J67,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K67,$A$12:$A$87,0)),0))</f>
-        <v>46485</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F67,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G67,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H67,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I67,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J67,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K67,$A$12:$A$95,0)),0))</f>
+        <v>46497</v>
       </c>
       <c r="M67" s="18">
         <f>IF(E67=0,IF(COUNTA(F67:K67)=0,$D$2,L67),WORKDAY.INTL(L67,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46488</v>
+        <v>46498</v>
       </c>
       <c r="N67" s="18">
         <f>IF(E67=0,M67,WORKDAY.INTL(M67,E67-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46520</v>
+        <v>46512</v>
       </c>
       <c r="O67" s="19"/>
       <c r="P67" s="15" t="s">
@@ -5204,46 +5213,42 @@
     </row>
     <row r="68" spans="1:87">
       <c r="A68" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="B68" s="16" t="s">
         <v>232</v>
       </c>
-      <c r="B68" s="16" t="s">
+      <c r="C68" s="16" t="s">
         <v>233</v>
       </c>
-      <c r="C68" s="16" t="s">
-        <v>234</v>
-      </c>
       <c r="D68" s="17">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E68" s="15">
         <f>IF(D68=0,0,MAX(1,ROUNDUP(D68/$D$6,0)))</f>
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F68" s="15" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="G68" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="H68" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="I68" s="15" t="s">
-        <v>110</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="H68" s="15"/>
+      <c r="I68" s="15"/>
       <c r="J68" s="15"/>
       <c r="K68" s="15"/>
       <c r="L68" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F68,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G68,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H68,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I68,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J68,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K68,$A$12:$A$87,0)),0))</f>
-        <v>46560</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F68,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G68,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H68,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I68,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J68,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K68,$A$12:$A$95,0)),0))</f>
+        <v>46561</v>
       </c>
       <c r="M68" s="18">
         <f>IF(E68=0,IF(COUNTA(F68:K68)=0,$D$2,L68),WORKDAY.INTL(L68,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46561</v>
+        <v>46562</v>
       </c>
       <c r="N68" s="18">
         <f>IF(E68=0,M68,WORKDAY.INTL(M68,E68-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46575</v>
+        <v>46568</v>
       </c>
       <c r="O68" s="19"/>
       <c r="P68" s="15" t="s">
@@ -5252,163 +5257,211 @@
     </row>
     <row r="69" spans="1:87">
       <c r="A69" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="B69" s="16" t="s">
         <v>235</v>
       </c>
-      <c r="B69" s="16" t="s">
-        <v>236</v>
-      </c>
       <c r="C69" s="16" t="s">
-        <v>237</v>
+        <v>146</v>
       </c>
       <c r="D69" s="17">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E69" s="15">
         <f>IF(D69=0,0,MAX(1,ROUNDUP(D69/$D$6,0)))</f>
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F69" s="15" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G69" s="15" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="H69" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="I69" s="15"/>
+        <v>231</v>
+      </c>
+      <c r="I69" s="15" t="s">
+        <v>226</v>
+      </c>
       <c r="J69" s="15"/>
       <c r="K69" s="15"/>
       <c r="L69" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F69,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G69,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H69,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I69,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J69,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K69,$A$12:$A$87,0)),0))</f>
-        <v>46560</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F69,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G69,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H69,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I69,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J69,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K69,$A$12:$A$95,0)),0))</f>
+        <v>46568</v>
       </c>
       <c r="M69" s="18">
         <f>IF(E69=0,IF(COUNTA(F69:K69)=0,$D$2,L69),WORKDAY.INTL(L69,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46561</v>
+        <v>46569</v>
       </c>
       <c r="N69" s="18">
         <f>IF(E69=0,M69,WORKDAY.INTL(M69,E69-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46583</v>
-      </c>
-      <c r="O69" s="19" t="s">
-        <v>90</v>
-      </c>
+        <v>46576</v>
+      </c>
+      <c r="O69" s="19"/>
       <c r="P69" s="15" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="70" spans="1:87">
-      <c r="A70" s="15" t="s">
-        <v>238</v>
-      </c>
-      <c r="B70" s="16" t="s">
-        <v>239</v>
-      </c>
-      <c r="C70" s="16" t="s">
-        <v>240</v>
-      </c>
-      <c r="D70" s="17">
-        <v>15</v>
-      </c>
-      <c r="E70" s="15">
-        <f>IF(D70=0,0,MAX(1,ROUNDUP(D70/$D$6,0)))</f>
-        <v>21</v>
-      </c>
-      <c r="F70" s="15" t="s">
-        <v>235</v>
-      </c>
-      <c r="G70" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="H70" s="15" t="s">
-        <v>232</v>
-      </c>
-      <c r="I70" s="15" t="s">
-        <v>220</v>
-      </c>
-      <c r="J70" s="15"/>
-      <c r="K70" s="15"/>
-      <c r="L70" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F70,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G70,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H70,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I70,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J70,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K70,$A$12:$A$87,0)),0))</f>
-        <v>46583</v>
-      </c>
-      <c r="M70" s="18">
-        <f>IF(E70=0,IF(COUNTA(F70:K70)=0,$D$2,L70),WORKDAY.INTL(L70,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46586</v>
-      </c>
-      <c r="N70" s="18">
-        <f>IF(E70=0,M70,WORKDAY.INTL(M70,E70-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46614</v>
-      </c>
-      <c r="O70" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="P70" s="15" t="s">
-        <v>91</v>
-      </c>
+      <c r="A70" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="B70" s="13"/>
+      <c r="C70" s="13"/>
+      <c r="D70" s="13"/>
+      <c r="E70" s="13"/>
+      <c r="F70" s="13"/>
+      <c r="G70" s="13"/>
+      <c r="H70" s="13"/>
+      <c r="I70" s="13"/>
+      <c r="J70" s="13"/>
+      <c r="K70" s="13"/>
+      <c r="L70" s="13"/>
+      <c r="M70" s="13"/>
+      <c r="N70" s="13"/>
+      <c r="O70" s="13"/>
+      <c r="P70" s="13"/>
+      <c r="R70" s="14"/>
+      <c r="S70" s="14"/>
+      <c r="T70" s="14"/>
+      <c r="U70" s="14"/>
+      <c r="V70" s="14"/>
+      <c r="W70" s="14"/>
+      <c r="X70" s="14"/>
+      <c r="Y70" s="14"/>
+      <c r="Z70" s="14"/>
+      <c r="AA70" s="14"/>
+      <c r="AB70" s="14"/>
+      <c r="AC70" s="14"/>
+      <c r="AD70" s="14"/>
+      <c r="AE70" s="14"/>
+      <c r="AF70" s="14"/>
+      <c r="AG70" s="14"/>
+      <c r="AH70" s="14"/>
+      <c r="AI70" s="14"/>
+      <c r="AJ70" s="14"/>
+      <c r="AK70" s="14"/>
+      <c r="AL70" s="14"/>
+      <c r="AM70" s="14"/>
+      <c r="AN70" s="14"/>
+      <c r="AO70" s="14"/>
+      <c r="AP70" s="14"/>
+      <c r="AQ70" s="14"/>
+      <c r="AR70" s="14"/>
+      <c r="AS70" s="14"/>
+      <c r="AT70" s="14"/>
+      <c r="AU70" s="14"/>
+      <c r="AV70" s="14"/>
+      <c r="AW70" s="14"/>
+      <c r="AX70" s="14"/>
+      <c r="AY70" s="14"/>
+      <c r="AZ70" s="14"/>
+      <c r="BA70" s="14"/>
+      <c r="BB70" s="14"/>
+      <c r="BC70" s="14"/>
+      <c r="BD70" s="14"/>
+      <c r="BE70" s="14"/>
+      <c r="BF70" s="14"/>
+      <c r="BG70" s="14"/>
+      <c r="BH70" s="14"/>
+      <c r="BI70" s="14"/>
+      <c r="BJ70" s="14"/>
+      <c r="BK70" s="14"/>
+      <c r="BL70" s="14"/>
+      <c r="BM70" s="14"/>
+      <c r="BN70" s="14"/>
+      <c r="BO70" s="14"/>
+      <c r="BP70" s="14"/>
+      <c r="BQ70" s="14"/>
+      <c r="BR70" s="14"/>
+      <c r="BS70" s="14"/>
+      <c r="BT70" s="14"/>
+      <c r="BU70" s="14"/>
+      <c r="BV70" s="14"/>
+      <c r="BW70" s="14"/>
+      <c r="BX70" s="14"/>
+      <c r="BY70" s="14"/>
+      <c r="BZ70" s="14"/>
+      <c r="CA70" s="14"/>
+      <c r="CB70" s="14"/>
+      <c r="CC70" s="14"/>
+      <c r="CD70" s="14"/>
+      <c r="CE70" s="14"/>
+      <c r="CF70" s="14"/>
+      <c r="CG70" s="14"/>
+      <c r="CH70" s="14"/>
+      <c r="CI70" s="14"/>
     </row>
     <row r="71" spans="1:87">
       <c r="A71" s="15" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B71" s="16" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C71" s="16" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D71" s="17">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E71" s="15">
         <f>IF(D71=0,0,MAX(1,ROUNDUP(D71/$D$6,0)))</f>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F71" s="15" t="s">
-        <v>238</v>
-      </c>
-      <c r="G71" s="15"/>
-      <c r="H71" s="15"/>
-      <c r="I71" s="15"/>
+        <v>206</v>
+      </c>
+      <c r="G71" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="H71" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="I71" s="15" t="s">
+        <v>242</v>
+      </c>
       <c r="J71" s="15"/>
       <c r="K71" s="15"/>
       <c r="L71" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F71,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G71,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H71,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I71,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J71,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K71,$A$12:$A$87,0)),0))</f>
-        <v>46614</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F71,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G71,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H71,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I71,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J71,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K71,$A$12:$A$95,0)),0))</f>
+        <v>46560</v>
       </c>
       <c r="M71" s="18">
         <f>IF(E71=0,IF(COUNTA(F71:K71)=0,$D$2,L71),WORKDAY.INTL(L71,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46615</v>
+        <v>46561</v>
       </c>
       <c r="N71" s="18">
         <f>IF(E71=0,M71,WORKDAY.INTL(M71,E71-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46629</v>
-      </c>
-      <c r="O71" s="19"/>
+        <v>46583</v>
+      </c>
+      <c r="O71" s="19" t="s">
+        <v>90</v>
+      </c>
       <c r="P71" s="15" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="72" spans="1:87">
+    <row r="72" spans="1:87" ht="26" customHeight="1">
       <c r="A72" s="15" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B72" s="16" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C72" s="16" t="s">
-        <v>246</v>
+        <v>192</v>
       </c>
       <c r="D72" s="17">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E72" s="15">
-        <f>IF(D72=0,0,MAX(1,ROUNDUP(D72/$D$6,0)))</f>
-        <v>5</v>
+        <f>D72</f>
+        <v>8</v>
       </c>
       <c r="F72" s="15" t="s">
-        <v>238</v>
+        <v>206</v>
       </c>
       <c r="G72" s="15"/>
       <c r="H72" s="15"/>
@@ -5416,62 +5469,62 @@
       <c r="J72" s="15"/>
       <c r="K72" s="15"/>
       <c r="L72" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F72,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G72,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H72,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I72,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J72,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K72,$A$12:$A$87,0)),0))</f>
-        <v>46614</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F72,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G72,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H72,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I72,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J72,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K72,$A$12:$A$95,0)),0))</f>
+        <v>46533</v>
       </c>
       <c r="M72" s="18">
         <f>IF(E72=0,IF(COUNTA(F72:K72)=0,$D$2,L72),WORKDAY.INTL(L72,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46615</v>
+        <v>46534</v>
       </c>
       <c r="N72" s="18">
         <f>IF(E72=0,M72,WORKDAY.INTL(M72,E72-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46621</v>
+        <v>46545</v>
       </c>
       <c r="O72" s="19"/>
       <c r="P72" s="15" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="73" spans="1:87">
       <c r="A73" s="15" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B73" s="16" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C73" s="16" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D73" s="17">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E73" s="15">
         <f>IF(D73=0,0,MAX(1,ROUNDUP(D73/$D$6,0)))</f>
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F73" s="15" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="G73" s="15" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="H73" s="15" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="I73" s="15"/>
       <c r="J73" s="15"/>
       <c r="K73" s="15"/>
       <c r="L73" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F73,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G73,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H73,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I73,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J73,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K73,$A$12:$A$87,0)),0))</f>
-        <v>46614</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F73,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G73,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H73,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I73,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J73,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K73,$A$12:$A$95,0)),0))</f>
+        <v>46533</v>
       </c>
       <c r="M73" s="18">
         <f>IF(E73=0,IF(COUNTA(F73:K73)=0,$D$2,L73),WORKDAY.INTL(L73,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46615</v>
+        <v>46534</v>
       </c>
       <c r="N73" s="18">
         <f>IF(E73=0,M73,WORKDAY.INTL(M73,E73-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46629</v>
+        <v>46560</v>
       </c>
       <c r="O73" s="19" t="s">
         <v>90</v>
@@ -5481,133 +5534,87 @@
       </c>
     </row>
     <row r="74" spans="1:87">
-      <c r="A74" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="B74" s="13"/>
-      <c r="C74" s="13"/>
-      <c r="D74" s="13"/>
-      <c r="E74" s="13"/>
-      <c r="F74" s="13"/>
-      <c r="G74" s="13"/>
-      <c r="H74" s="13"/>
-      <c r="I74" s="13"/>
-      <c r="J74" s="13"/>
-      <c r="K74" s="13"/>
-      <c r="L74" s="13"/>
-      <c r="M74" s="13"/>
-      <c r="N74" s="13"/>
-      <c r="O74" s="13"/>
-      <c r="P74" s="13"/>
-      <c r="R74" s="14"/>
-      <c r="S74" s="14"/>
-      <c r="T74" s="14"/>
-      <c r="U74" s="14"/>
-      <c r="V74" s="14"/>
-      <c r="W74" s="14"/>
-      <c r="X74" s="14"/>
-      <c r="Y74" s="14"/>
-      <c r="Z74" s="14"/>
-      <c r="AA74" s="14"/>
-      <c r="AB74" s="14"/>
-      <c r="AC74" s="14"/>
-      <c r="AD74" s="14"/>
-      <c r="AE74" s="14"/>
-      <c r="AF74" s="14"/>
-      <c r="AG74" s="14"/>
-      <c r="AH74" s="14"/>
-      <c r="AI74" s="14"/>
-      <c r="AJ74" s="14"/>
-      <c r="AK74" s="14"/>
-      <c r="AL74" s="14"/>
-      <c r="AM74" s="14"/>
-      <c r="AN74" s="14"/>
-      <c r="AO74" s="14"/>
-      <c r="AP74" s="14"/>
-      <c r="AQ74" s="14"/>
-      <c r="AR74" s="14"/>
-      <c r="AS74" s="14"/>
-      <c r="AT74" s="14"/>
-      <c r="AU74" s="14"/>
-      <c r="AV74" s="14"/>
-      <c r="AW74" s="14"/>
-      <c r="AX74" s="14"/>
-      <c r="AY74" s="14"/>
-      <c r="AZ74" s="14"/>
-      <c r="BA74" s="14"/>
-      <c r="BB74" s="14"/>
-      <c r="BC74" s="14"/>
-      <c r="BD74" s="14"/>
-      <c r="BE74" s="14"/>
-      <c r="BF74" s="14"/>
-      <c r="BG74" s="14"/>
-      <c r="BH74" s="14"/>
-      <c r="BI74" s="14"/>
-      <c r="BJ74" s="14"/>
-      <c r="BK74" s="14"/>
-      <c r="BL74" s="14"/>
-      <c r="BM74" s="14"/>
-      <c r="BN74" s="14"/>
-      <c r="BO74" s="14"/>
-      <c r="BP74" s="14"/>
-      <c r="BQ74" s="14"/>
-      <c r="BR74" s="14"/>
-      <c r="BS74" s="14"/>
-      <c r="BT74" s="14"/>
-      <c r="BU74" s="14"/>
-      <c r="BV74" s="14"/>
-      <c r="BW74" s="14"/>
-      <c r="BX74" s="14"/>
-      <c r="BY74" s="14"/>
-      <c r="BZ74" s="14"/>
-      <c r="CA74" s="14"/>
-      <c r="CB74" s="14"/>
-      <c r="CC74" s="14"/>
-      <c r="CD74" s="14"/>
-      <c r="CE74" s="14"/>
-      <c r="CF74" s="14"/>
-      <c r="CG74" s="14"/>
-      <c r="CH74" s="14"/>
-      <c r="CI74" s="14"/>
+      <c r="A74" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="B74" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="C74" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="D74" s="17">
+        <v>8</v>
+      </c>
+      <c r="E74" s="15">
+        <f>IF(D74=0,0,MAX(1,ROUNDUP(D74/$D$6,0)))</f>
+        <v>11</v>
+      </c>
+      <c r="F74" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="G74" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="H74" s="15"/>
+      <c r="I74" s="15"/>
+      <c r="J74" s="15"/>
+      <c r="K74" s="15"/>
+      <c r="L74" s="18">
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F74,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G74,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H74,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I74,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J74,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K74,$A$12:$A$95,0)),0))</f>
+        <v>46488</v>
+      </c>
+      <c r="M74" s="18">
+        <f>IF(E74=0,IF(COUNTA(F74:K74)=0,$D$2,L74),WORKDAY.INTL(L74,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
+        <v>46489</v>
+      </c>
+      <c r="N74" s="18">
+        <f>IF(E74=0,M74,WORKDAY.INTL(M74,E74-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
+        <v>46504</v>
+      </c>
+      <c r="O74" s="19"/>
+      <c r="P74" s="15" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="75" spans="1:87">
       <c r="A75" s="15" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B75" s="16" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C75" s="16" t="s">
-        <v>103</v>
+        <v>250</v>
       </c>
       <c r="D75" s="17">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E75" s="15">
         <f>IF(D75=0,0,MAX(1,ROUNDUP(D75/$D$6,0)))</f>
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="F75" s="15" t="s">
-        <v>101</v>
+        <v>214</v>
       </c>
       <c r="G75" s="15" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H75" s="15"/>
       <c r="I75" s="15"/>
       <c r="J75" s="15"/>
       <c r="K75" s="15"/>
       <c r="L75" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F75,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G75,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H75,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I75,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J75,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K75,$A$12:$A$87,0)),0))</f>
-        <v>46390</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F75,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G75,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H75,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I75,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J75,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K75,$A$12:$A$95,0)),0))</f>
+        <v>46485</v>
       </c>
       <c r="M75" s="18">
         <f>IF(E75=0,IF(COUNTA(F75:K75)=0,$D$2,L75),WORKDAY.INTL(L75,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46391</v>
+        <v>46488</v>
       </c>
       <c r="N75" s="18">
         <f>IF(E75=0,M75,WORKDAY.INTL(M75,E75-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46399</v>
+        <v>46520</v>
       </c>
       <c r="O75" s="19"/>
       <c r="P75" s="15" t="s">
@@ -5616,40 +5623,46 @@
     </row>
     <row r="76" spans="1:87">
       <c r="A76" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="B76" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="C76" s="16" t="s">
         <v>253</v>
       </c>
-      <c r="B76" s="16" t="s">
-        <v>254</v>
-      </c>
-      <c r="C76" s="16" t="s">
-        <v>255</v>
-      </c>
       <c r="D76" s="17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E76" s="15">
         <f>IF(D76=0,0,MAX(1,ROUNDUP(D76/$D$6,0)))</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F76" s="15" t="s">
-        <v>212</v>
-      </c>
-      <c r="G76" s="15"/>
-      <c r="H76" s="15"/>
-      <c r="I76" s="15"/>
+        <v>240</v>
+      </c>
+      <c r="G76" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="H76" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="I76" s="15" t="s">
+        <v>116</v>
+      </c>
       <c r="J76" s="15"/>
       <c r="K76" s="15"/>
       <c r="L76" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F76,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G76,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H76,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I76,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J76,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K76,$A$12:$A$87,0)),0))</f>
-        <v>46513</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F76,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G76,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H76,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I76,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J76,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K76,$A$12:$A$95,0)),0))</f>
+        <v>46560</v>
       </c>
       <c r="M76" s="18">
         <f>IF(E76=0,IF(COUNTA(F76:K76)=0,$D$2,L76),WORKDAY.INTL(L76,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46516</v>
+        <v>46561</v>
       </c>
       <c r="N76" s="18">
         <f>IF(E76=0,M76,WORKDAY.INTL(M76,E76-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46538</v>
+        <v>46575</v>
       </c>
       <c r="O76" s="19"/>
       <c r="P76" s="15" t="s">
@@ -5658,179 +5671,145 @@
     </row>
     <row r="77" spans="1:87">
       <c r="A77" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="B77" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="C77" s="16" t="s">
         <v>256</v>
       </c>
-      <c r="B77" s="16" t="s">
-        <v>257</v>
-      </c>
-      <c r="C77" s="16" t="s">
-        <v>258</v>
-      </c>
       <c r="D77" s="17">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E77" s="15">
         <f>IF(D77=0,0,MAX(1,ROUNDUP(D77/$D$6,0)))</f>
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F77" s="15" t="s">
-        <v>253</v>
-      </c>
-      <c r="G77" s="15"/>
-      <c r="H77" s="15"/>
+        <v>237</v>
+      </c>
+      <c r="G77" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="H77" s="15" t="s">
+        <v>113</v>
+      </c>
       <c r="I77" s="15"/>
       <c r="J77" s="15"/>
       <c r="K77" s="15"/>
       <c r="L77" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F77,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G77,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H77,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I77,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J77,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K77,$A$12:$A$87,0)),0))</f>
-        <v>46538</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F77,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G77,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H77,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I77,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J77,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K77,$A$12:$A$95,0)),0))</f>
+        <v>46583</v>
       </c>
       <c r="M77" s="18">
         <f>IF(E77=0,IF(COUNTA(F77:K77)=0,$D$2,L77),WORKDAY.INTL(L77,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46539</v>
+        <v>46586</v>
       </c>
       <c r="N77" s="18">
         <f>IF(E77=0,M77,WORKDAY.INTL(M77,E77-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46552</v>
-      </c>
-      <c r="O77" s="19"/>
+        <v>46608</v>
+      </c>
+      <c r="O77" s="19" t="s">
+        <v>90</v>
+      </c>
       <c r="P77" s="15" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="78" spans="1:87">
       <c r="A78" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="B78" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="C78" s="16" t="s">
         <v>259</v>
       </c>
-      <c r="B78" s="16" t="s">
-        <v>260</v>
-      </c>
-      <c r="C78" s="16" t="s">
-        <v>261</v>
-      </c>
       <c r="D78" s="17">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E78" s="15">
         <f>IF(D78=0,0,MAX(1,ROUNDUP(D78/$D$6,0)))</f>
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F78" s="15" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G78" s="15" t="s">
-        <v>229</v>
-      </c>
-      <c r="H78" s="15"/>
-      <c r="I78" s="15"/>
-      <c r="J78" s="15"/>
+        <v>241</v>
+      </c>
+      <c r="H78" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="I78" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="J78" s="15" t="s">
+        <v>226</v>
+      </c>
       <c r="K78" s="15"/>
       <c r="L78" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F78,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G78,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H78,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I78,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J78,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K78,$A$12:$A$87,0)),0))</f>
-        <v>46552</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F78,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G78,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H78,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I78,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J78,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K78,$A$12:$A$95,0)),0))</f>
+        <v>46608</v>
       </c>
       <c r="M78" s="18">
         <f>IF(E78=0,IF(COUNTA(F78:K78)=0,$D$2,L78),WORKDAY.INTL(L78,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46553</v>
+        <v>46609</v>
       </c>
       <c r="N78" s="18">
         <f>IF(E78=0,M78,WORKDAY.INTL(M78,E78-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46573</v>
-      </c>
-      <c r="O78" s="19"/>
+        <v>46637</v>
+      </c>
+      <c r="O78" s="19" t="s">
+        <v>90</v>
+      </c>
       <c r="P78" s="15" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="79" spans="1:87">
-      <c r="A79" s="13" t="s">
+      <c r="A79" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="B79" s="16" t="s">
+        <v>261</v>
+      </c>
+      <c r="C79" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="B79" s="13"/>
-      <c r="C79" s="13"/>
-      <c r="D79" s="13"/>
-      <c r="E79" s="13"/>
-      <c r="F79" s="13"/>
-      <c r="G79" s="13"/>
-      <c r="H79" s="13"/>
-      <c r="I79" s="13"/>
-      <c r="J79" s="13"/>
-      <c r="K79" s="13"/>
-      <c r="L79" s="13"/>
-      <c r="M79" s="13"/>
-      <c r="N79" s="13"/>
-      <c r="O79" s="13"/>
-      <c r="P79" s="13"/>
-      <c r="R79" s="14"/>
-      <c r="S79" s="14"/>
-      <c r="T79" s="14"/>
-      <c r="U79" s="14"/>
-      <c r="V79" s="14"/>
-      <c r="W79" s="14"/>
-      <c r="X79" s="14"/>
-      <c r="Y79" s="14"/>
-      <c r="Z79" s="14"/>
-      <c r="AA79" s="14"/>
-      <c r="AB79" s="14"/>
-      <c r="AC79" s="14"/>
-      <c r="AD79" s="14"/>
-      <c r="AE79" s="14"/>
-      <c r="AF79" s="14"/>
-      <c r="AG79" s="14"/>
-      <c r="AH79" s="14"/>
-      <c r="AI79" s="14"/>
-      <c r="AJ79" s="14"/>
-      <c r="AK79" s="14"/>
-      <c r="AL79" s="14"/>
-      <c r="AM79" s="14"/>
-      <c r="AN79" s="14"/>
-      <c r="AO79" s="14"/>
-      <c r="AP79" s="14"/>
-      <c r="AQ79" s="14"/>
-      <c r="AR79" s="14"/>
-      <c r="AS79" s="14"/>
-      <c r="AT79" s="14"/>
-      <c r="AU79" s="14"/>
-      <c r="AV79" s="14"/>
-      <c r="AW79" s="14"/>
-      <c r="AX79" s="14"/>
-      <c r="AY79" s="14"/>
-      <c r="AZ79" s="14"/>
-      <c r="BA79" s="14"/>
-      <c r="BB79" s="14"/>
-      <c r="BC79" s="14"/>
-      <c r="BD79" s="14"/>
-      <c r="BE79" s="14"/>
-      <c r="BF79" s="14"/>
-      <c r="BG79" s="14"/>
-      <c r="BH79" s="14"/>
-      <c r="BI79" s="14"/>
-      <c r="BJ79" s="14"/>
-      <c r="BK79" s="14"/>
-      <c r="BL79" s="14"/>
-      <c r="BM79" s="14"/>
-      <c r="BN79" s="14"/>
-      <c r="BO79" s="14"/>
-      <c r="BP79" s="14"/>
-      <c r="BQ79" s="14"/>
-      <c r="BR79" s="14"/>
-      <c r="BS79" s="14"/>
-      <c r="BT79" s="14"/>
-      <c r="BU79" s="14"/>
-      <c r="BV79" s="14"/>
-      <c r="BW79" s="14"/>
-      <c r="BX79" s="14"/>
-      <c r="BY79" s="14"/>
-      <c r="BZ79" s="14"/>
-      <c r="CA79" s="14"/>
-      <c r="CB79" s="14"/>
-      <c r="CC79" s="14"/>
-      <c r="CD79" s="14"/>
-      <c r="CE79" s="14"/>
-      <c r="CF79" s="14"/>
-      <c r="CG79" s="14"/>
-      <c r="CH79" s="14"/>
-      <c r="CI79" s="14"/>
+      <c r="D79" s="17">
+        <v>8</v>
+      </c>
+      <c r="E79" s="15">
+        <f>IF(D79=0,0,MAX(1,ROUNDUP(D79/$D$6,0)))</f>
+        <v>11</v>
+      </c>
+      <c r="F79" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="G79" s="15"/>
+      <c r="H79" s="15"/>
+      <c r="I79" s="15"/>
+      <c r="J79" s="15"/>
+      <c r="K79" s="15"/>
+      <c r="L79" s="18">
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F79,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G79,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H79,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I79,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J79,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K79,$A$12:$A$95,0)),0))</f>
+        <v>46637</v>
+      </c>
+      <c r="M79" s="18">
+        <f>IF(E79=0,IF(COUNTA(F79:K79)=0,$D$2,L79),WORKDAY.INTL(L79,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
+        <v>46638</v>
+      </c>
+      <c r="N79" s="18">
+        <f>IF(E79=0,M79,WORKDAY.INTL(M79,E79-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
+        <v>46652</v>
+      </c>
+      <c r="O79" s="19"/>
+      <c r="P79" s="15" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="80" spans="1:87">
       <c r="A80" s="15" t="s">
@@ -5840,7 +5819,7 @@
         <v>264</v>
       </c>
       <c r="C80" s="16" t="s">
-        <v>187</v>
+        <v>265</v>
       </c>
       <c r="D80" s="17">
         <v>3</v>
@@ -5850,72 +5829,70 @@
         <v>5</v>
       </c>
       <c r="F80" s="15" t="s">
-        <v>241</v>
-      </c>
-      <c r="G80" s="15" t="s">
-        <v>244</v>
-      </c>
-      <c r="H80" s="15" t="s">
-        <v>235</v>
-      </c>
-      <c r="I80" s="15" t="s">
-        <v>251</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="G80" s="15"/>
+      <c r="H80" s="15"/>
+      <c r="I80" s="15"/>
       <c r="J80" s="15"/>
       <c r="K80" s="15"/>
       <c r="L80" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F80,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G80,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H80,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I80,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J80,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K80,$A$12:$A$87,0)),0))</f>
-        <v>46629</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F80,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G80,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H80,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I80,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J80,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K80,$A$12:$A$95,0)),0))</f>
+        <v>46637</v>
       </c>
       <c r="M80" s="18">
         <f>IF(E80=0,IF(COUNTA(F80:K80)=0,$D$2,L80),WORKDAY.INTL(L80,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46630</v>
+        <v>46638</v>
       </c>
       <c r="N80" s="18">
         <f>IF(E80=0,M80,WORKDAY.INTL(M80,E80-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46636</v>
+        <v>46644</v>
       </c>
       <c r="O80" s="19"/>
       <c r="P80" s="15" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="81" spans="1:16">
+    <row r="81" spans="1:87">
       <c r="A81" s="15" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B81" s="16" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C81" s="16" t="s">
-        <v>89</v>
+        <v>268</v>
       </c>
       <c r="D81" s="17">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E81" s="15">
         <f>IF(D81=0,0,MAX(1,ROUNDUP(D81/$D$6,0)))</f>
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F81" s="15" t="s">
-        <v>247</v>
-      </c>
-      <c r="G81" s="15"/>
-      <c r="H81" s="15"/>
+        <v>257</v>
+      </c>
+      <c r="G81" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="H81" s="15" t="s">
+        <v>113</v>
+      </c>
       <c r="I81" s="15"/>
       <c r="J81" s="15"/>
       <c r="K81" s="15"/>
       <c r="L81" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F81,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G81,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H81,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I81,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J81,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K81,$A$12:$A$87,0)),0))</f>
-        <v>46629</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F81,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G81,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H81,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I81,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J81,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K81,$A$12:$A$95,0)),0))</f>
+        <v>46637</v>
       </c>
       <c r="M81" s="18">
         <f>IF(E81=0,IF(COUNTA(F81:K81)=0,$D$2,L81),WORKDAY.INTL(L81,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46630</v>
+        <v>46638</v>
       </c>
       <c r="N81" s="18">
         <f>IF(E81=0,M81,WORKDAY.INTL(M81,E81-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46637</v>
+        <v>46652</v>
       </c>
       <c r="O81" s="19" t="s">
         <v>90</v>
@@ -5924,167 +5901,203 @@
         <v>91</v>
       </c>
     </row>
-    <row r="82" spans="1:16">
-      <c r="A82" s="15" t="s">
-        <v>267</v>
-      </c>
-      <c r="B82" s="16" t="s">
-        <v>268</v>
-      </c>
-      <c r="C82" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="D82" s="17">
-        <v>3</v>
-      </c>
-      <c r="E82" s="15">
-        <f>IF(D82=0,0,MAX(1,ROUNDUP(D82/$D$6,0)))</f>
+    <row r="82" spans="1:87">
+      <c r="A82" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="B82" s="13"/>
+      <c r="C82" s="13"/>
+      <c r="D82" s="13"/>
+      <c r="E82" s="13"/>
+      <c r="F82" s="13"/>
+      <c r="G82" s="13"/>
+      <c r="H82" s="13"/>
+      <c r="I82" s="13"/>
+      <c r="J82" s="13"/>
+      <c r="K82" s="13"/>
+      <c r="L82" s="13"/>
+      <c r="M82" s="13"/>
+      <c r="N82" s="13"/>
+      <c r="O82" s="13"/>
+      <c r="P82" s="13"/>
+      <c r="R82" s="14"/>
+      <c r="S82" s="14"/>
+      <c r="T82" s="14"/>
+      <c r="U82" s="14"/>
+      <c r="V82" s="14"/>
+      <c r="W82" s="14"/>
+      <c r="X82" s="14"/>
+      <c r="Y82" s="14"/>
+      <c r="Z82" s="14"/>
+      <c r="AA82" s="14"/>
+      <c r="AB82" s="14"/>
+      <c r="AC82" s="14"/>
+      <c r="AD82" s="14"/>
+      <c r="AE82" s="14"/>
+      <c r="AF82" s="14"/>
+      <c r="AG82" s="14"/>
+      <c r="AH82" s="14"/>
+      <c r="AI82" s="14"/>
+      <c r="AJ82" s="14"/>
+      <c r="AK82" s="14"/>
+      <c r="AL82" s="14"/>
+      <c r="AM82" s="14"/>
+      <c r="AN82" s="14"/>
+      <c r="AO82" s="14"/>
+      <c r="AP82" s="14"/>
+      <c r="AQ82" s="14"/>
+      <c r="AR82" s="14"/>
+      <c r="AS82" s="14"/>
+      <c r="AT82" s="14"/>
+      <c r="AU82" s="14"/>
+      <c r="AV82" s="14"/>
+      <c r="AW82" s="14"/>
+      <c r="AX82" s="14"/>
+      <c r="AY82" s="14"/>
+      <c r="AZ82" s="14"/>
+      <c r="BA82" s="14"/>
+      <c r="BB82" s="14"/>
+      <c r="BC82" s="14"/>
+      <c r="BD82" s="14"/>
+      <c r="BE82" s="14"/>
+      <c r="BF82" s="14"/>
+      <c r="BG82" s="14"/>
+      <c r="BH82" s="14"/>
+      <c r="BI82" s="14"/>
+      <c r="BJ82" s="14"/>
+      <c r="BK82" s="14"/>
+      <c r="BL82" s="14"/>
+      <c r="BM82" s="14"/>
+      <c r="BN82" s="14"/>
+      <c r="BO82" s="14"/>
+      <c r="BP82" s="14"/>
+      <c r="BQ82" s="14"/>
+      <c r="BR82" s="14"/>
+      <c r="BS82" s="14"/>
+      <c r="BT82" s="14"/>
+      <c r="BU82" s="14"/>
+      <c r="BV82" s="14"/>
+      <c r="BW82" s="14"/>
+      <c r="BX82" s="14"/>
+      <c r="BY82" s="14"/>
+      <c r="BZ82" s="14"/>
+      <c r="CA82" s="14"/>
+      <c r="CB82" s="14"/>
+      <c r="CC82" s="14"/>
+      <c r="CD82" s="14"/>
+      <c r="CE82" s="14"/>
+      <c r="CF82" s="14"/>
+      <c r="CG82" s="14"/>
+      <c r="CH82" s="14"/>
+      <c r="CI82" s="14"/>
+    </row>
+    <row r="83" spans="1:87">
+      <c r="A83" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="B83" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="C83" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="D83" s="17">
         <v>5</v>
       </c>
-      <c r="F82" s="15" t="s">
-        <v>238</v>
-      </c>
-      <c r="G82" s="15" t="s">
-        <v>247</v>
-      </c>
-      <c r="H82" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="I82" s="15" t="s">
-        <v>217</v>
-      </c>
-      <c r="J82" s="15" t="s">
-        <v>214</v>
-      </c>
-      <c r="K82" s="15"/>
-      <c r="L82" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F82,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G82,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H82,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I82,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J82,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K82,$A$12:$A$87,0)),0))</f>
-        <v>46629</v>
-      </c>
-      <c r="M82" s="18">
-        <f>IF(E82=0,IF(COUNTA(F82:K82)=0,$D$2,L82),WORKDAY.INTL(L82,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46630</v>
-      </c>
-      <c r="N82" s="18">
-        <f>IF(E82=0,M82,WORKDAY.INTL(M82,E82-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46636</v>
-      </c>
-      <c r="O82" s="19"/>
-      <c r="P82" s="15" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="83" spans="1:16">
-      <c r="A83" s="15" t="s">
-        <v>269</v>
-      </c>
-      <c r="B83" s="16" t="s">
-        <v>270</v>
-      </c>
-      <c r="C83" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="D83" s="17">
-        <v>3</v>
-      </c>
       <c r="E83" s="15">
-        <f>D83</f>
-        <v>3</v>
+        <f>IF(D83=0,0,MAX(1,ROUNDUP(D83/$D$6,0)))</f>
+        <v>7</v>
       </c>
       <c r="F83" s="15" t="s">
-        <v>263</v>
+        <v>101</v>
       </c>
       <c r="G83" s="15" t="s">
-        <v>265</v>
-      </c>
-      <c r="H83" s="15" t="s">
-        <v>267</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="H83" s="15"/>
       <c r="I83" s="15"/>
       <c r="J83" s="15"/>
       <c r="K83" s="15"/>
       <c r="L83" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F83,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G83,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H83,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I83,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J83,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K83,$A$12:$A$87,0)),0))</f>
-        <v>46637</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F83,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G83,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H83,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I83,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J83,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K83,$A$12:$A$95,0)),0))</f>
+        <v>46390</v>
       </c>
       <c r="M83" s="18">
         <f>IF(E83=0,IF(COUNTA(F83:K83)=0,$D$2,L83),WORKDAY.INTL(L83,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46638</v>
+        <v>46391</v>
       </c>
       <c r="N83" s="18">
         <f>IF(E83=0,M83,WORKDAY.INTL(M83,E83-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46642</v>
-      </c>
-      <c r="O83" s="19" t="s">
-        <v>90</v>
-      </c>
+        <v>46399</v>
+      </c>
+      <c r="O83" s="19"/>
       <c r="P83" s="15" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="84" spans="1:16">
+    <row r="84" spans="1:87">
       <c r="A84" s="15" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B84" s="16" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C84" s="16" t="s">
-        <v>89</v>
+        <v>274</v>
       </c>
       <c r="D84" s="17">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E84" s="15">
         <f>IF(D84=0,0,MAX(1,ROUNDUP(D84/$D$6,0)))</f>
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F84" s="15" t="s">
-        <v>269</v>
-      </c>
-      <c r="G84" s="15"/>
+        <v>222</v>
+      </c>
+      <c r="G84" s="15" t="s">
+        <v>178</v>
+      </c>
       <c r="H84" s="15"/>
       <c r="I84" s="15"/>
       <c r="J84" s="15"/>
       <c r="K84" s="15"/>
       <c r="L84" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F84,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G84,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H84,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I84,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J84,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K84,$A$12:$A$87,0)),0))</f>
-        <v>46642</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F84,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G84,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H84,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I84,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J84,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K84,$A$12:$A$95,0)),0))</f>
+        <v>46490</v>
       </c>
       <c r="M84" s="18">
         <f>IF(E84=0,IF(COUNTA(F84:K84)=0,$D$2,L84),WORKDAY.INTL(L84,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46643</v>
+        <v>46491</v>
       </c>
       <c r="N84" s="18">
         <f>IF(E84=0,M84,WORKDAY.INTL(M84,E84-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46666</v>
-      </c>
-      <c r="O84" s="19" t="s">
-        <v>90</v>
-      </c>
+        <v>46511</v>
+      </c>
+      <c r="O84" s="19"/>
       <c r="P84" s="15" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="85" spans="1:16" ht="26" customHeight="1">
+    <row r="85" spans="1:87">
       <c r="A85" s="15" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B85" s="16" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C85" s="16" t="s">
-        <v>89</v>
+        <v>277</v>
       </c>
       <c r="D85" s="17">
+        <v>7</v>
+      </c>
+      <c r="E85" s="15">
+        <f>IF(D85=0,0,MAX(1,ROUNDUP(D85/$D$6,0)))</f>
         <v>10</v>
       </c>
-      <c r="E85" s="15">
-        <f>D85</f>
-        <v>10</v>
-      </c>
       <c r="F85" s="15" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="G85" s="15"/>
       <c r="H85" s="15"/>
@@ -6092,177 +6105,589 @@
       <c r="J85" s="15"/>
       <c r="K85" s="15"/>
       <c r="L85" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F85,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G85,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H85,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I85,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J85,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K85,$A$12:$A$87,0)),0))</f>
-        <v>46642</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F85,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G85,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H85,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I85,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J85,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K85,$A$12:$A$95,0)),0))</f>
+        <v>46511</v>
       </c>
       <c r="M85" s="18">
         <f>IF(E85=0,IF(COUNTA(F85:K85)=0,$D$2,L85),WORKDAY.INTL(L85,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46643</v>
+        <v>46512</v>
       </c>
       <c r="N85" s="18">
         <f>IF(E85=0,M85,WORKDAY.INTL(M85,E85-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46656</v>
+        <v>46531</v>
       </c>
       <c r="O85" s="19"/>
       <c r="P85" s="15" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="86" spans="1:16">
+    <row r="86" spans="1:87">
       <c r="A86" s="15" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B86" s="16" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C86" s="16" t="s">
-        <v>89</v>
+        <v>280</v>
       </c>
       <c r="D86" s="17">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E86" s="15">
         <f>IF(D86=0,0,MAX(1,ROUNDUP(D86/$D$6,0)))</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F86" s="15" t="s">
-        <v>271</v>
-      </c>
-      <c r="G86" s="15"/>
+        <v>275</v>
+      </c>
+      <c r="G86" s="15" t="s">
+        <v>248</v>
+      </c>
       <c r="H86" s="15"/>
       <c r="I86" s="15"/>
       <c r="J86" s="15"/>
       <c r="K86" s="15"/>
       <c r="L86" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F86,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G86,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H86,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I86,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J86,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K86,$A$12:$A$87,0)),0))</f>
-        <v>46666</v>
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F86,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G86,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H86,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I86,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J86,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K86,$A$12:$A$95,0)),0))</f>
+        <v>46531</v>
       </c>
       <c r="M86" s="18">
         <f>IF(E86=0,IF(COUNTA(F86:K86)=0,$D$2,L86),WORKDAY.INTL(L86,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46666</v>
+        <v>46532</v>
       </c>
       <c r="N86" s="18">
         <f>IF(E86=0,M86,WORKDAY.INTL(M86,E86-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46666</v>
+        <v>46552</v>
       </c>
       <c r="O86" s="19"/>
       <c r="P86" s="15" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="87" spans="1:16">
-      <c r="A87" s="15" t="s">
-        <v>277</v>
-      </c>
-      <c r="B87" s="16" t="s">
+    <row r="87" spans="1:87">
+      <c r="A87" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="B87" s="13"/>
+      <c r="C87" s="13"/>
+      <c r="D87" s="13"/>
+      <c r="E87" s="13"/>
+      <c r="F87" s="13"/>
+      <c r="G87" s="13"/>
+      <c r="H87" s="13"/>
+      <c r="I87" s="13"/>
+      <c r="J87" s="13"/>
+      <c r="K87" s="13"/>
+      <c r="L87" s="13"/>
+      <c r="M87" s="13"/>
+      <c r="N87" s="13"/>
+      <c r="O87" s="13"/>
+      <c r="P87" s="13"/>
+      <c r="R87" s="14"/>
+      <c r="S87" s="14"/>
+      <c r="T87" s="14"/>
+      <c r="U87" s="14"/>
+      <c r="V87" s="14"/>
+      <c r="W87" s="14"/>
+      <c r="X87" s="14"/>
+      <c r="Y87" s="14"/>
+      <c r="Z87" s="14"/>
+      <c r="AA87" s="14"/>
+      <c r="AB87" s="14"/>
+      <c r="AC87" s="14"/>
+      <c r="AD87" s="14"/>
+      <c r="AE87" s="14"/>
+      <c r="AF87" s="14"/>
+      <c r="AG87" s="14"/>
+      <c r="AH87" s="14"/>
+      <c r="AI87" s="14"/>
+      <c r="AJ87" s="14"/>
+      <c r="AK87" s="14"/>
+      <c r="AL87" s="14"/>
+      <c r="AM87" s="14"/>
+      <c r="AN87" s="14"/>
+      <c r="AO87" s="14"/>
+      <c r="AP87" s="14"/>
+      <c r="AQ87" s="14"/>
+      <c r="AR87" s="14"/>
+      <c r="AS87" s="14"/>
+      <c r="AT87" s="14"/>
+      <c r="AU87" s="14"/>
+      <c r="AV87" s="14"/>
+      <c r="AW87" s="14"/>
+      <c r="AX87" s="14"/>
+      <c r="AY87" s="14"/>
+      <c r="AZ87" s="14"/>
+      <c r="BA87" s="14"/>
+      <c r="BB87" s="14"/>
+      <c r="BC87" s="14"/>
+      <c r="BD87" s="14"/>
+      <c r="BE87" s="14"/>
+      <c r="BF87" s="14"/>
+      <c r="BG87" s="14"/>
+      <c r="BH87" s="14"/>
+      <c r="BI87" s="14"/>
+      <c r="BJ87" s="14"/>
+      <c r="BK87" s="14"/>
+      <c r="BL87" s="14"/>
+      <c r="BM87" s="14"/>
+      <c r="BN87" s="14"/>
+      <c r="BO87" s="14"/>
+      <c r="BP87" s="14"/>
+      <c r="BQ87" s="14"/>
+      <c r="BR87" s="14"/>
+      <c r="BS87" s="14"/>
+      <c r="BT87" s="14"/>
+      <c r="BU87" s="14"/>
+      <c r="BV87" s="14"/>
+      <c r="BW87" s="14"/>
+      <c r="BX87" s="14"/>
+      <c r="BY87" s="14"/>
+      <c r="BZ87" s="14"/>
+      <c r="CA87" s="14"/>
+      <c r="CB87" s="14"/>
+      <c r="CC87" s="14"/>
+      <c r="CD87" s="14"/>
+      <c r="CE87" s="14"/>
+      <c r="CF87" s="14"/>
+      <c r="CG87" s="14"/>
+      <c r="CH87" s="14"/>
+      <c r="CI87" s="14"/>
+    </row>
+    <row r="88" spans="1:87">
+      <c r="A88" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="B88" s="16" t="s">
+        <v>283</v>
+      </c>
+      <c r="C88" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="D88" s="17">
+        <v>3</v>
+      </c>
+      <c r="E88" s="15">
+        <f>IF(D88=0,0,MAX(1,ROUNDUP(D88/$D$6,0)))</f>
+        <v>5</v>
+      </c>
+      <c r="F88" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="G88" s="15" t="s">
+        <v>263</v>
+      </c>
+      <c r="H88" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="I88" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="J88" s="15"/>
+      <c r="K88" s="15"/>
+      <c r="L88" s="18">
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F88,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G88,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H88,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I88,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J88,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K88,$A$12:$A$95,0)),0))</f>
+        <v>46652</v>
+      </c>
+      <c r="M88" s="18">
+        <f>IF(E88=0,IF(COUNTA(F88:K88)=0,$D$2,L88),WORKDAY.INTL(L88,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
+        <v>46653</v>
+      </c>
+      <c r="N88" s="18">
+        <f>IF(E88=0,M88,WORKDAY.INTL(M88,E88-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
+        <v>46659</v>
+      </c>
+      <c r="O88" s="19"/>
+      <c r="P88" s="15" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="89" spans="1:87">
+      <c r="A89" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="B89" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="C89" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D89" s="17">
+        <v>4</v>
+      </c>
+      <c r="E89" s="15">
+        <f>IF(D89=0,0,MAX(1,ROUNDUP(D89/$D$6,0)))</f>
+        <v>6</v>
+      </c>
+      <c r="F89" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="G89" s="15"/>
+      <c r="H89" s="15"/>
+      <c r="I89" s="15"/>
+      <c r="J89" s="15"/>
+      <c r="K89" s="15"/>
+      <c r="L89" s="18">
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F89,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G89,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H89,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I89,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J89,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K89,$A$12:$A$95,0)),0))</f>
+        <v>46652</v>
+      </c>
+      <c r="M89" s="18">
+        <f>IF(E89=0,IF(COUNTA(F89:K89)=0,$D$2,L89),WORKDAY.INTL(L89,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
+        <v>46653</v>
+      </c>
+      <c r="N89" s="18">
+        <f>IF(E89=0,M89,WORKDAY.INTL(M89,E89-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
+        <v>46660</v>
+      </c>
+      <c r="O89" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="P89" s="15" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="90" spans="1:87">
+      <c r="A90" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="B90" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="C90" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D90" s="17">
+        <v>3</v>
+      </c>
+      <c r="E90" s="15">
+        <f>IF(D90=0,0,MAX(1,ROUNDUP(D90/$D$6,0)))</f>
+        <v>5</v>
+      </c>
+      <c r="F90" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="G90" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="H90" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="C87" s="16" t="s">
+      <c r="I90" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="J90" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="K90" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="L90" s="18">
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F90,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G90,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H90,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I90,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J90,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K90,$A$12:$A$95,0)),0))</f>
+        <v>46652</v>
+      </c>
+      <c r="M90" s="18">
+        <f>IF(E90=0,IF(COUNTA(F90:K90)=0,$D$2,L90),WORKDAY.INTL(L90,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
+        <v>46653</v>
+      </c>
+      <c r="N90" s="18">
+        <f>IF(E90=0,M90,WORKDAY.INTL(M90,E90-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
+        <v>46659</v>
+      </c>
+      <c r="O90" s="19"/>
+      <c r="P90" s="15" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="91" spans="1:87">
+      <c r="A91" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="B91" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="C91" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="D87" s="17">
+      <c r="D91" s="17">
+        <v>3</v>
+      </c>
+      <c r="E91" s="15">
+        <f>D91</f>
+        <v>3</v>
+      </c>
+      <c r="F91" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="G91" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="H91" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="I91" s="15"/>
+      <c r="J91" s="15"/>
+      <c r="K91" s="15"/>
+      <c r="L91" s="18">
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F91,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G91,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H91,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I91,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J91,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K91,$A$12:$A$95,0)),0))</f>
+        <v>46660</v>
+      </c>
+      <c r="M91" s="18">
+        <f>IF(E91=0,IF(COUNTA(F91:K91)=0,$D$2,L91),WORKDAY.INTL(L91,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
+        <v>46664</v>
+      </c>
+      <c r="N91" s="18">
+        <f>IF(E91=0,M91,WORKDAY.INTL(M91,E91-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
+        <v>46666</v>
+      </c>
+      <c r="O91" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="P91" s="15" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="92" spans="1:87">
+      <c r="A92" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="B92" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="C92" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D92" s="17">
+        <v>12</v>
+      </c>
+      <c r="E92" s="15">
+        <f>IF(D92=0,0,MAX(1,ROUNDUP(D92/$D$6,0)))</f>
+        <v>17</v>
+      </c>
+      <c r="F92" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="G92" s="15"/>
+      <c r="H92" s="15"/>
+      <c r="I92" s="15"/>
+      <c r="J92" s="15"/>
+      <c r="K92" s="15"/>
+      <c r="L92" s="18">
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F92,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G92,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H92,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I92,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J92,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K92,$A$12:$A$95,0)),0))</f>
+        <v>46666</v>
+      </c>
+      <c r="M92" s="18">
+        <f>IF(E92=0,IF(COUNTA(F92:K92)=0,$D$2,L92),WORKDAY.INTL(L92,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
+        <v>46667</v>
+      </c>
+      <c r="N92" s="18">
+        <f>IF(E92=0,M92,WORKDAY.INTL(M92,E92-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
+        <v>46692</v>
+      </c>
+      <c r="O92" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="P92" s="15" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" spans="1:87" ht="26" customHeight="1">
+      <c r="A93" s="15" t="s">
+        <v>292</v>
+      </c>
+      <c r="B93" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="C93" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D93" s="17">
+        <v>10</v>
+      </c>
+      <c r="E93" s="15">
+        <f>D93</f>
+        <v>10</v>
+      </c>
+      <c r="F93" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="G93" s="15"/>
+      <c r="H93" s="15"/>
+      <c r="I93" s="15"/>
+      <c r="J93" s="15"/>
+      <c r="K93" s="15"/>
+      <c r="L93" s="18">
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F93,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G93,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H93,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I93,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J93,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K93,$A$12:$A$95,0)),0))</f>
+        <v>46666</v>
+      </c>
+      <c r="M93" s="18">
+        <f>IF(E93=0,IF(COUNTA(F93:K93)=0,$D$2,L93),WORKDAY.INTL(L93,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
+        <v>46667</v>
+      </c>
+      <c r="N93" s="18">
+        <f>IF(E93=0,M93,WORKDAY.INTL(M93,E93-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
+        <v>46681</v>
+      </c>
+      <c r="O93" s="19"/>
+      <c r="P93" s="15" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="94" spans="1:87">
+      <c r="A94" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="B94" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="C94" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D94" s="17">
+        <v>0</v>
+      </c>
+      <c r="E94" s="15">
+        <f>IF(D94=0,0,MAX(1,ROUNDUP(D94/$D$6,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="F94" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="G94" s="15"/>
+      <c r="H94" s="15"/>
+      <c r="I94" s="15"/>
+      <c r="J94" s="15"/>
+      <c r="K94" s="15"/>
+      <c r="L94" s="18">
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F94,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G94,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H94,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I94,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J94,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K94,$A$12:$A$95,0)),0))</f>
+        <v>46692</v>
+      </c>
+      <c r="M94" s="18">
+        <f>IF(E94=0,IF(COUNTA(F94:K94)=0,$D$2,L94),WORKDAY.INTL(L94,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
+        <v>46692</v>
+      </c>
+      <c r="N94" s="18">
+        <f>IF(E94=0,M94,WORKDAY.INTL(M94,E94-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
+        <v>46692</v>
+      </c>
+      <c r="O94" s="19"/>
+      <c r="P94" s="15" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="95" spans="1:87">
+      <c r="A95" s="15" t="s">
+        <v>296</v>
+      </c>
+      <c r="B95" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="C95" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D95" s="17">
         <v>30</v>
       </c>
-      <c r="E87" s="15">
-        <f>D87</f>
+      <c r="E95" s="15">
+        <f>D95</f>
         <v>30</v>
       </c>
-      <c r="F87" s="15" t="s">
-        <v>273</v>
-      </c>
-      <c r="G87" s="15" t="s">
-        <v>271</v>
-      </c>
-      <c r="H87" s="15"/>
-      <c r="I87" s="15"/>
-      <c r="J87" s="15"/>
-      <c r="K87" s="15"/>
-      <c r="L87" s="18">
-        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$87,MATCH(F87,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(G87,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(H87,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(I87,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(J87,$A$12:$A$87,0)),0),IFERROR(INDEX($N$12:$N$87,MATCH(K87,$A$12:$A$87,0)),0))</f>
-        <v>46666</v>
-      </c>
-      <c r="M87" s="18">
-        <f>IF(E87=0,IF(COUNTA(F87:K87)=0,$D$2,L87),WORKDAY.INTL(L87,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46667</v>
-      </c>
-      <c r="N87" s="18">
-        <f>IF(E87=0,M87,WORKDAY.INTL(M87,E87-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
-        <v>46709</v>
-      </c>
-      <c r="O87" s="19"/>
-      <c r="P87" s="15" t="s">
+      <c r="F95" s="15" t="s">
+        <v>292</v>
+      </c>
+      <c r="G95" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="H95" s="15"/>
+      <c r="I95" s="15"/>
+      <c r="J95" s="15"/>
+      <c r="K95" s="15"/>
+      <c r="L95" s="18">
+        <f>MAX($D$2-1,IFERROR(INDEX($N$12:$N$95,MATCH(F95,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(G95,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(H95,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(I95,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(J95,$A$12:$A$95,0)),0),IFERROR(INDEX($N$12:$N$95,MATCH(K95,$A$12:$A$95,0)),0))</f>
+        <v>46692</v>
+      </c>
+      <c r="M95" s="18">
+        <f>IF(E95=0,IF(COUNTA(F95:K95)=0,$D$2,L95),WORKDAY.INTL(L95,1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
+        <v>46693</v>
+      </c>
+      <c r="N95" s="18">
+        <f>IF(E95=0,M95,WORKDAY.INTL(M95,E95-1,$D$3,'לוח שנה וחגים'!$F$5:$F$48))</f>
+        <v>46734</v>
+      </c>
+      <c r="O95" s="19"/>
+      <c r="P95" s="15" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="89" spans="1:16">
-      <c r="B89" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="N89" s="20">
-        <f>N86</f>
-        <v>46666</v>
-      </c>
-    </row>
-    <row r="90" spans="1:16">
-      <c r="B90" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="N90" s="20">
-        <f>N87</f>
-        <v>46709</v>
-      </c>
-    </row>
-    <row r="91" spans="1:16">
-      <c r="B91" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="N91" s="21">
-        <f>ROUND((N89-$D$2+1)/7,1)</f>
-        <v>47.6</v>
-      </c>
-    </row>
-    <row r="92" spans="1:16">
-      <c r="B92" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="N92" s="21">
-        <f>NETWORKDAYS.INTL($D$2,N89,$D$3,'לוח שנה וחגים'!$F$5:$F$48)</f>
-        <v>225</v>
-      </c>
-    </row>
-    <row r="93" spans="1:16">
-      <c r="B93" s="22" t="s">
-        <v>282</v>
-      </c>
-      <c r="C93" s="22"/>
-      <c r="D93" s="22"/>
-      <c r="E93" s="22"/>
-      <c r="F93" s="22"/>
-      <c r="G93" s="22"/>
-      <c r="H93" s="22"/>
-      <c r="I93" s="22"/>
-      <c r="J93" s="22"/>
-      <c r="K93" s="22"/>
-      <c r="L93" s="22"/>
-      <c r="M93" s="22"/>
-      <c r="N93" s="22"/>
-    </row>
-    <row r="94" spans="1:16">
-      <c r="B94" s="22" t="s">
-        <v>283</v>
-      </c>
-      <c r="C94" s="22"/>
-      <c r="D94" s="22"/>
-      <c r="E94" s="22"/>
-      <c r="F94" s="22"/>
-      <c r="G94" s="22"/>
-      <c r="H94" s="22"/>
-      <c r="I94" s="22"/>
-      <c r="J94" s="22"/>
-      <c r="K94" s="22"/>
-      <c r="L94" s="22"/>
-      <c r="M94" s="22"/>
-      <c r="N94" s="22"/>
+    <row r="97" spans="2:14">
+      <c r="B97" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="N97" s="20">
+        <f>N94</f>
+        <v>46692</v>
+      </c>
+    </row>
+    <row r="98" spans="2:14">
+      <c r="B98" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="N98" s="20">
+        <f>N95</f>
+        <v>46734</v>
+      </c>
+    </row>
+    <row r="99" spans="2:14">
+      <c r="B99" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="N99" s="21">
+        <f>ROUND((N97-$D$2+1)/7,1)</f>
+        <v>51.3</v>
+      </c>
+    </row>
+    <row r="100" spans="2:14">
+      <c r="B100" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="N100" s="21">
+        <f>NETWORKDAYS.INTL($D$2,N97,$D$3,'לוח שנה וחגים'!$F$5:$F$48)</f>
+        <v>242</v>
+      </c>
+    </row>
+    <row r="101" spans="2:14">
+      <c r="B101" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="C101" s="22"/>
+      <c r="D101" s="22"/>
+      <c r="E101" s="22"/>
+      <c r="F101" s="22"/>
+      <c r="G101" s="22"/>
+      <c r="H101" s="22"/>
+      <c r="I101" s="22"/>
+      <c r="J101" s="22"/>
+      <c r="K101" s="22"/>
+      <c r="L101" s="22"/>
+      <c r="M101" s="22"/>
+      <c r="N101" s="22"/>
+    </row>
+    <row r="102" spans="2:14">
+      <c r="B102" s="22" t="s">
+        <v>302</v>
+      </c>
+      <c r="C102" s="22"/>
+      <c r="D102" s="22"/>
+      <c r="E102" s="22"/>
+      <c r="F102" s="22"/>
+      <c r="G102" s="22"/>
+      <c r="H102" s="22"/>
+      <c r="I102" s="22"/>
+      <c r="J102" s="22"/>
+      <c r="K102" s="22"/>
+      <c r="L102" s="22"/>
+      <c r="M102" s="22"/>
+      <c r="N102" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -6272,24 +6697,24 @@
     <mergeCell ref="A8:P8"/>
     <mergeCell ref="A9:P9"/>
     <mergeCell ref="A12:P12"/>
-    <mergeCell ref="A21:P21"/>
-    <mergeCell ref="A25:P25"/>
-    <mergeCell ref="A37:P37"/>
-    <mergeCell ref="A44:P44"/>
-    <mergeCell ref="A50:P50"/>
-    <mergeCell ref="A58:P58"/>
-    <mergeCell ref="A63:P63"/>
-    <mergeCell ref="A74:P74"/>
-    <mergeCell ref="A79:P79"/>
-    <mergeCell ref="B93:N93"/>
-    <mergeCell ref="B94:N94"/>
+    <mergeCell ref="A23:P23"/>
+    <mergeCell ref="A27:P27"/>
+    <mergeCell ref="A39:P39"/>
+    <mergeCell ref="A47:P47"/>
+    <mergeCell ref="A54:P54"/>
+    <mergeCell ref="A62:P62"/>
+    <mergeCell ref="A70:P70"/>
+    <mergeCell ref="A82:P82"/>
+    <mergeCell ref="A87:P87"/>
+    <mergeCell ref="B101:N101"/>
+    <mergeCell ref="B102:N102"/>
   </mergeCells>
   <conditionalFormatting sqref="R11:CI11">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R12:CI87">
+  <conditionalFormatting sqref="R12:CI95">
     <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
       <formula>AND($E12=0,$A12&lt;&gt;"",$M12&gt;=R$10,$M12&lt;=R$10+6)</formula>
     </cfRule>
@@ -7311,18 +7736,18 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>284</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="9" t="s">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>287</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="60" customHeight="1">
@@ -7330,10 +7755,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>288</v>
+        <v>307</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>289</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="45" customHeight="1">
@@ -7341,10 +7766,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>290</v>
+        <v>309</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>291</v>
+        <v>310</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" customHeight="1">
@@ -7352,10 +7777,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>292</v>
+        <v>311</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>293</v>
+        <v>312</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="45" customHeight="1">
@@ -7363,10 +7788,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>294</v>
+        <v>313</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="45" customHeight="1">
@@ -7374,10 +7799,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>297</v>
+        <v>316</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" customHeight="1">
@@ -7385,10 +7810,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>298</v>
+        <v>317</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>299</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" customHeight="1">
@@ -7396,10 +7821,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>300</v>
+        <v>319</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30" customHeight="1">
@@ -7407,15 +7832,15 @@
         <v>8</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>302</v>
+        <v>321</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>303</v>
+        <v>322</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="22" t="s">
-        <v>304</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -7438,18 +7863,18 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>305</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="9" t="s">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>306</v>
+        <v>325</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="45" customHeight="1">
@@ -7457,10 +7882,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>307</v>
+        <v>326</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>308</v>
+        <v>327</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="60" customHeight="1">
@@ -7468,10 +7893,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>309</v>
+        <v>328</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>310</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="45" customHeight="1">
@@ -7479,10 +7904,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>311</v>
+        <v>330</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30" customHeight="1">
@@ -7490,10 +7915,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>313</v>
+        <v>332</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>314</v>
+        <v>333</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" customHeight="1">
@@ -7501,10 +7926,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>316</v>
+        <v>335</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" customHeight="1">
@@ -7512,10 +7937,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>317</v>
+        <v>336</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>318</v>
+        <v>337</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" customHeight="1">
@@ -7523,10 +7948,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>319</v>
+        <v>338</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>320</v>
+        <v>339</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30" customHeight="1">
@@ -7534,10 +7959,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>321</v>
+        <v>340</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>322</v>
+        <v>341</v>
       </c>
     </row>
   </sheetData>
